--- a/02_analyze-requirements/v1.1/CL-hoi-BA-v1.1.xlsx
+++ b/02_analyze-requirements/v1.1/CL-hoi-BA-v1.1.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -82,8 +82,28 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -118,21 +138,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF81ACA6"/>
         <bgColor rgb="FF9999FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +175,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -198,10 +203,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,21 +243,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,340 +515,350 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="1"/>
-    <col width="30" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="14" customWidth="1" style="11" min="4" max="4"/>
-    <col width="60" customWidth="1" style="11" min="5" max="5"/>
+    <col width="14" customWidth="1" style="14" min="1" max="1"/>
+    <col width="30" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="14" customWidth="1" style="14" min="4" max="4"/>
+    <col width="60" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Điểm chưa rõ cần hỏi lại BA — v1.1 (FoxEco)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Cập nhật 2026-09-16 sau khi BA trả lời lượt 1 (13 điểm) + rà sâu PRD ⟷ scenario từng chức năng. Mỗi module 1 sheet; điền câu trả lời BA trực tiếp vào sheet đó. Nguồn chi tiết: 02_analyze-requirements/v1.1/&lt;module&gt;/risk_assessment.md (và v1.0/FEED-bang-tin/). · Cập nhật 2026-09-16 (tối): USR đóng C-USR-05/06 theo câu trả lời BA; nhận file danh mục văn phòng (ghi chú ở HOME/FEED/ASN). · Cập nhật 2026-09-17: BA trả lời thêm HOME/FEED/GIFT/USR — đóng C-HOME-05, C-FEED-02/03/04, 2 dòng USR; vòng 2 C-HOME-04, C-HOME-06, C-GIFT-04; mở mới C-FEED-05 + đề nghị cập nhật PRD FEED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>⛔ FILE DẪN XUẤT (DERIVED) — KHÔNG PHẢI NGUỒN. Không sửa nghiệp vụ ở đây. Nguồn canonical của trạng thái CL là frontmatter counts: và bảng Clarifications ở 02_analyze-requirements/v1.1/&lt;MODULE&gt;/risk_assessment.md (FEED ở v1.0/FEED-bang-tin/). Lệch nhau ⇒ risk_assessment.md THẮNG. File này chỉ để GỬI BA đọc; sửa xong ở risk_assessment.md rồi mới đồng bộ xuống đây. Cập nhật 2026-09-17 (health-check G-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Chức năng</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Số điểm cần hỏi BA</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Mức ưu tiên</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú xử lý</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="75" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="75" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>ORD</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Đăng tin &amp; Quản lý tin</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao nhất</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-ORD-09 ('Tài liệu'). Vòng 2: C-ORD-04 (banner/điều khoản hàng cấm), C-ORD-13 (email mẫu HRIS — chặn 3 SC, 1 P1). Mới: C-ORD-14 (người nhận không có tài khoản → đơn kẹt) · 15 (biên 7 ngày/EXPIRED) · 16 (phạm vi sửa tin + OFFER) · 17 (gỡ/đăng lại).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>ĐÓNG HẾT 2026-09-17 (tối): C-ORD-18 Resolved — BA trả lời đủ 4 câu: (a) 3 mốc tiền là con số CHÍNH THỨC (b) nhãn chuẩn "Trọng lượng", GIỮ nhãn phụ Nhẹ/Trung bình/Nặng (c) LẤY UI LÀM CHUẨN ⇒ 3 trường Bước 1/3 là chip, PRD §8.1.4 ghi Dropdown là SAI (d) block Ghi chú đặt trước "Thông tin hàng" là đúng thiết kế, là textbox nhập được. Các CL cũ (C-ORD-04/09/13/14/15/16/17) đã đóng trước đó. ⇒ generate-tc assert CỨNG theo UI (SC-ORD-052/053 đã bỏ rào ghi-nhận).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>ACT</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Hoạt động (Đơn của tôi)</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-ACT-02 (nhãn theo app), C-ACT-01 (Đang diễn ra → Theo dõi đơn; Hoàn thành chưa tặng quà → Tặng quà). Mới: C-ACT-03 (đích tap card các ô còn lại) · C-ACT-04 (12 trạng thái chia 2 tab, đơn Đã huỷ ẩn/hiện, tin OFFER).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="C5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>generate-tc: chạy được cho toàn bộ 17 SC, KHÔNG còn giữ [GAP]. C-ACT-04 ĐÓNG 2026-09-17 — QA tự verify qua demo theo đúng chỉ dẫn BA (tab Hoạt động → Đang diễn ra): card OFFER title "Nhận giao hàng &lt;tuyến&gt;", badge "Chờ ghép", CTA "Chạm để xem tuyến đường của bạn".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>USR</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Tài khoản &amp; Hồ sơ</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>🟡 Còn 1 điểm</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>MỞ LẠI 2026-09-18: C-USR-07 — "địa chỉ mặc định để RỖNG có hợp lệ không, và có đường nào xoá địa chỉ đã lưu?". Đây là câu (v) của C-USR-05 mà BA chưa từng trả lời thẳng, nhưng C-USR-05 vẫn bị đóng Resolved 2026-09-16 =&gt; câu hỏi rơi mất; vibe-test VR-003 làm nổi lại bằng dữ kiện thực nghiệm (app cho lưu 2 lần với ô địa chỉ trống). — Phần đã chốt 2026-09-16 giữ nguyên: C-USR-05 (avatar chữ viết tắt; địa chỉ mặc định load HRIS + chọn từ danh sách), C-USR-06 (badge Hạng Đồng hành KHÔNG hiện). — 2026-09-18 (QC): "địa chỉ data hris luôn luôn có nhé... hiện tại ko có do bị bug không load data từ hris" =&gt; nhánh HRIS-trống KHÔNG tồn tại, ô rỗng là triệu chứng của BUG-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>✅ Hết điểm hỏi</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt 2026-09-16 (BA trả lời): C-USR-05 (avatar chữ viết tắt; địa chỉ mặc định load HRIS + chọn từ danh sách văn phòng; prefill giao hàng = người nhận, điểm xuất phát = người vận chuyển; kênh liên hệ bỏ hẳn) · C-USR-06 (badge "Hạng Đồng hành" không hiện). Đã chốt 2026-09-17: chuỗi lỗi SĐT giữ theo demo · BA nhận cập nhật PRD sau (theo dõi ở USR CHANGELOG Nợ #4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Trang chủ</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt 2026-09-17: C-HOME-05 (HIỆN empty state, không ẩn → SC-HOME-010 DEPRECATED). Vòng 2: C-HOME-04 (BA nói tin load toàn quốc ⟷ PRD lọc theo khu vực — câu trả lời tự mâu thuẫn) · C-HOME-06 (định nghĩa 'người tham gia', đơn Đã trả người gửi — thấp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>ĐÓNG HẾT 2026-09-17: C-HOME-04 vòng 3 (BA "giữ nguyên nhé" — chuỗi empty state EMP-01/EMP-04 giữ nguyên chữ PRD dù tin load toàn quốc) · C-HOME-05 · C-HOME-06 (Accepted). generate-tc: chạy được toàn bộ 28 SC, kể cả SC-HOME-019/025 nhánh 0 tin và SC-FEED-001/013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>FEED</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Bảng tin &amp; Chi tiết tin</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-FEED-01 (CTA chỉ ở Chi tiết tin; CÓ bản đồ). 2026-09-17: C-FEED-02 (placeholder + '0km', ảnh tĩnh vẽ tuyến) · C-FEED-03 (1 danh sách, không tab/lọc) · C-FEED-04 (trước ghép chỉ ẩn SĐT). Mới: C-FEED-05 (file toạ độ văn phòng lỗi — chặn Given SC-FEED-009) · đề nghị BA cập nhật PRD (7 chỗ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1" s="12">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="C8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>ĐÓNG HẾT 2026-09-17: C-FEED-01..05. Vế "gợi ý mở rộng khu vực" (EMP-04) đóng theo C-HOME-04 vòng 3 — BA chốt GIỮ NGUYÊN chữ PRD. Chỉ còn hành động "đề nghị BA cập nhật PRD" (7 chỗ) — BA đã đồng ý, chờ BA sửa tài liệu, không chặn generate-tc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1" s="15">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>ASN</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Ghép nối</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-ASN-03 (ghi đè = lỗi demo), C-NTF-02 (không có trần/ngày → '5 thông báo/1 tin OFFER'). Mới: C-ASN-04 (định nghĩa rule 5 thông báo) · C-ASN-05 (so khớp 'trùng điểm' với địa chỉ tự do — chặn data SC-ASN-011) · C-ASN-06 (câu thông báo, thấp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1" s="12">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Đã chốt hết 2026-09-17: C-ASN-03 (ghi đè = lỗi demo) · C-NTF-02 (5 thông báo/1 tin OFFER) · C-ASN-04 (định nghĩa đủ rule 5 thông báo, trần độc lập theo từng tuyến) · C-ASN-05 (so khớp địa chỉ = chính xác, theo danh mục văn phòng) · C-ASN-06 (bỏ qua, dùng câu có sẵn trong 15 thông báo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1" s="15">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>DLV</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Giao nhận &amp; Theo dõi đơn</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-DLV-02 (không có GPS). Mới: C-DLV-05 (cơ chế hẹn giao lại + timeline) · C-DLV-06 (3 cấu trúc màn 'Không liên lạc được' — SC-DLV-043 dễ FAIL oan) · C-DLV-07 (nhắc/chuyển admin) · C-DLV-08 (giao quầy 2 đường).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1" s="12">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi BA</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>ĐÓNG HẾT điểm cần BA 2026-09-17: C-DLV-05/06 (vibe-check demo) · C-DLV-07 (BA: CHỈ gửi remind; "chuyển admin hỗ trợ" OUT OF SCOPE v1.1) · C-DLV-08 câu (d) (role admin chưa làm phase này). CÒN 1 VIỆC CỦA QA (không hỏi BA): C-DLV-08 (a)(b) — vibe-check block LỊCH SỬ khi chọn quầy trực tiếp để chốt cờ/NTF-05⟷NTF-11 cho SC-DLV-039 ⟷ SC-DLV-045.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1" s="15">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>TS</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Trust &amp; Safety (Báo sự cố)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Sheet mới. C-TS-02 (nút Báo sự cố hiện ở trạng thái nào; đơn vào 'Có sự cố' bằng cách nào khi dev xử lý tay) · C-TS-03 (prefill 1 hay 9 trường, mã đơn sửa được?, Custom Tabs có làm được nút Thử lại).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1" s="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="C11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>generate-tc: chạy được cho toàn bộ 15 SC. C-TS-03 ĐÓNG 2026-09-17 — Dev trả lời: nút "Thử lại" khi mất mạng do CHÍNH APP hiển thị, không phụ thuộc công nghệ WebView/Custom Tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1" s="15">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>NTF</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Thông báo</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-NTF-03 (mark-all). Mới: C-NTF-04 (màn đích khi chạm từng loại thông báo — DoD #7 bắt test) · C-NTF-05 (người nhận thông báo khi huỷ nhận / giao uỷ quyền-quầy).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1" s="12">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Đã chốt hết 2026-09-17: C-NTF-03 (mark-all) · C-NTF-04 (v1.1 mọi loại → Theo dõi đơn; chạm 1 tin tự đánh dấu đã đọc riêng; đơn không tồn tại thì báo lỗi riêng) · C-NTF-05 (Carrier huỷ nhận báo cả 2 bên; giao quầy/uỷ quyền có thêm NTF-05 nhắc xác nhận; huỷ khi Chờ ghép chỉ báo người nhận).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1" s="15">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>GIFT</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Quà cảm ơn</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Đã chốt: C-GIFT-02 (lỗi demo; back về màn trước). 2026-09-17: C-GIFT-04 chốt tặng 1 lần → vòng 2: 'tặng sau' mâu thuẫn C-ACT-01 + nhãn nút sau khi tặng + đích NTF-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1" s="12">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="C13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>✅ Hết điểm hỏi</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Đã chốt hết 2026-09-17: C-GIFT-02 (lỗi demo) và C-GIFT-04 (BA trả lời đủ (1)(2)(3)(4) — mỗi đơn tặng 1 lần, không giới hạn thời gian vào lại tặng, nút đổi 'Bạn đã đánh giá' + disable, tap card đã tặng → Theo dõi đơn, NTF-06 phân theo đã/chưa tặng). Vibe-check demo không tới được màn xác nhận 'đã đánh giá' do ô tải ảnh bằng chứng ở bước giao hàng không mở được trình chọn file trong bản demo này — không ảnh hưởng việc đóng CL vì đã có câu trả lời BA bằng lời.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1" s="15">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>CNL</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Huỷ đơn / Huỷ nhận đơn</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>✅ Hết điểm hỏi</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Đã chốt: C-CNL-03 (không có tool admin, dev xử lý tay). Rủi ro vận hành đơn 'Có sự cố' treo → Accepted, ghi vào test report. Câu 'đơn vào Có sự cố thế nào' chuyển sang TS (C-TS-02).</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="12">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Tổng cộng (cập nhật 2026-09-17): Lượt 1 (2026-09-16) BA trả lời 13 điểm + USR vòng 2. Lượt 2026-09-17 BA trả lời thêm 9 dòng (USR 2 · HOME 3 · FEED 3 · GIFT 1) → 6 đã chốt, 3 cần hỏi vòng 2; phát sinh 1 câu mới (C-FEED-05) + 1 đề nghị cập nhật PRD (FEED). Còn 24 điểm cần BA trả lời trên 9 module (USR, CNL đã hết). Ưu tiên hỏi trước các dòng ghi '🔴 Cao'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="12"/>
+    <row r="15" ht="15" customHeight="1" s="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Tổng cộng (cập nhật 2026-09-17 tối, sau khi rà soát TOÀN BỘ workbook — không chỉ các mục nhắc demo): Lượt 1 (2026-09-16) BA trả lời 13 điểm + USR vòng 2. Lượt 2026-09-17 (sáng) BA trả lời thêm 9 dòng. Lượt 2026-09-17 (chiều) vibe-check demo QA GiangDC2 qua Playwright MCP, đóng 5 điểm bằng bằng chứng UI thật + đồng bộ vào canonical risk_assessment.md (trước đó chỉ có ở xlsx). Lượt 2026-09-17 (tối) rà soát lại TỪNG DÒNG của TẤT CẢ sheet — phát hiện 12 dòng BA đã trả lời đầy đủ nhưng chưa đóng sổ, xử lý xong 11/12. ASN và NTF nay HẾT điểm hỏi (thêm USR, CNL, GIFT đã hết trước đó — tổng 5/11 module xong). Còn lại 9 điểm cần BA trả lời trên 6 module (ORD·ACT·HOME mỗi module còn đúng 1 câu nhỏ do giới hạn demo; FEED chỉ còn chờ BA cập nhật PRD; DLV còn 4 — module nặng nhất; TS còn 1, chờ Dev xác nhận kỹ thuật). Ưu tiên hỏi trước các dòng ghi '🔴 Cao' (nay chỉ còn ở DLV). · Cập nhật 2026-09-17 (đêm, QA GiangDC2 tự vibe-check qua Chrome MCP theo đúng chỉ dẫn BA "kiểm tra lại qua mcp"): ĐÓNG THÊM 5 điểm — C-TS-03 (Dev: nút Thử lại do app hiển thị), C-DLV-05 (timeline 5 mốc cố định), C-DLV-06 (2 ô quầy bắt buộc, form chặn submit khi trống), C-ORD-16 + C-ACT-04 (card tin OFFER quan sát được qua demo khi vào đúng tab Hoạt động → Đang diễn ra, thay vì màn Theo dõi đơn bị giới hạn demo che khuất). 8/11 module nay HẾT điểm hỏi BA: USR · CNL · GIFT · ASN · NTF · ORD · ACT · TS. CHỈ CÒN 3 điểm thật sự cần BA/Dev trả lời: C-DLV-07 (🔴 Cao — nhắc/chuyển admin hỗ trợ) · C-DLV-08 câu (c) (thời hạn giữ hàng đường trực tiếp) · C-HOME-04 vòng 3 (chuỗi empty state khi không lọc khu vực). Xem đúng 3 dòng đó ở sheet DLV/HOME, cột "Câu hỏi cụ thể cho BA" — sẵn sàng gửi BA. · CẬP NHẬT 2026-09-17 (vòng cuối — BA trả lời 3 điểm treo còn lại, QC GiangDC2 chuyển lời): ĐÓNG C-DLV-07 ("không chỉ gởi remind thôi nhé" = CHỈ gửi remind, không đổi trạng thái/nhãn/cờ) · C-HOME-04 vòng 3 ("giữ nguyên nhé" — chuỗi empty state giữ chữ PRD) · C-DLV-08 câu (d) ("phase này các chỗ liên quan đến role admin chưa làm nhé"). ⇒ 11/11 MODULE HẾT ĐIỂM CẦN HỎI BA — không còn dòng nào chờ BA trả lời trong workbook này. KẾT LUẬN SCOPE ÁP CHO TOÀN v1.1: mọi bề mặt role admin ("chuyển admin hỗ trợ", hạn giữ hàng tại quầy 4h/24h) là OUT OF SCOPE v1.1 — không viết assert, không log bug khi không thấy. Việc duy nhất còn lại là của QA, không phải của BA: vibe-check block LỊCH SỬ cho C-DLV-08 (a)(b). · CẬP NHẬT 2026-09-17 (chiều muộn): QC cung cấp ảnh UI wizard Bước 1/3 "Thông tin hàng" → MỞ C-ORD-18 (sheet ORD, dòng cuối) — 4 điểm UI lệch PRD §8.1.4, trong đó nặng nhất là MỐC TIỀN của 3 mức Giá trị hàng chưa có ở bất kỳ tài liệu nào. Trạng thái: 10/11 module hết điểm hỏi BA; còn ORD 1 điểm (C-ORD-18). Việc của QA (không hỏi BA): vibe-check block LỊCH SỬ cho C-DLV-08 (a)(b) + vibe-check bấm thật wizard Bước 1 để chốt trạng thái nút "Tiếp theo". · ⛔ CẬP NHẬT CUỐI 2026-09-17 (tối) — DÒNG NÀY THAY THẾ MỌI TRẠNG THÁI KỂ Ở TRÊN: C-ORD-18 đã Resolved cùng ngày (BA: lấy UI làm chuẩn cho 3 trường Bước 1/3) ⇒ 11/11 MODULE HẾT ĐIỂM HỎI BA, 0 CL Open trong toàn bộ v1.1. Còn đúng 1 CL Partially: C-DLV-08 (a)(b) — QA TỰ xác minh qua vibe-check block LỊCH SỬ, KHÔNG hỏi BA nữa. ⚠️ Các đoạn phía trên là NHẬT KÝ THEO MỐC THỜI GIAN (đọc để hiểu diễn biến), ⛔ không trích làm trạng thái hiện hành — trạng thái hiện hành đọc ở &lt;MODULE&gt;/risk_assessment.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="15">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>📐 CÁCH DỰNG LẠI FILE NÀY (nếu lệch canonical): đọc bảng Clarifications ở từng 02_analyze-requirements/v1.1/&lt;MODULE&gt;/risk_assessment.md, lọc dòng Status ≠ Resolved, đổ vào sheet theo module. ⛔ Không sửa ngược từ file này lên risk_assessment.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
@@ -851,226 +879,240 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>NTF-thong-bao — Thông báo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-NTF-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Cơ chế "Đánh dấu đã đọc" — bấm nút là mark-all (đánh dấu tất cả) hay mark-per-item (đánh dấu từng cái)? Đã thử vibe-test 2 cách trên demo 2026-09-15 nhưng demo là dữ liệu tĩnh/mock, không nối logic thật nên KHÔNG kết luận được.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-06 KP-01 §8 KB-NTF-01 (suy từ ảnh Figma, chưa chứng minh được cơ chế)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Nút "Đánh dấu đã đọc" hoạt động theo cơ chế nào — đánh dấu tất cả 1 lần hay từng thông báo riêng lẻ? PRD v1.1 không đề cập gì thêm tới cơ chế này.</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-NTF-011 chỉ ghi nhận cơ chế thực tế; SC-NTF-013 (chuông đồng bộ) khó assert nhất quán vì bước "đọc hết" chưa xác định</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Click vao đánh dấu tất cả là đã đọc nhé </t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Bấm 'Đánh dấu đã đọc' = đánh dấu TẤT CẢ đã đọc (mark-all). SC-NTF-011 hết GAP; SC-NTF-013 badge chuông về 0 sau khi bấm. Câu 'chạm 1 thông báo có đánh dấu riêng nó' → C-NTF-04.
 — Ghi chú cũ: Đã thử vibe-test qua demo 2026-09-15 — không dùng kết quả đó làm bằng chứng, cần hỏi BA hoặc verify trên STG thật</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-NTF-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>PRD chỉ nói 'chạm vào mở đúng đơn/màn liên quan' và chỉ nêu đích của NTF-07 (Trang cá nhân), trong khi DoD #7 bắt test 'mở đúng màn đích' cho cả 15 loại.</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.13 Post-Conditions · NTF-07 (tr.47) · §11 DoD #7 (tr.56)</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) Xin bảng màn đích khi chạm từng loại NTF-01..15 (vd NTF-03 → chi tiết đơn có nút 'Nhận giao'; NTF-06 với Người gửi → Theo dõi đơn hay thẳng màn Tặng quà; NTF-09 → đơn hết hạn hay wizard đăng lại).
 (b) Chạm 1 thông báo có tự đánh dấu RIÊNG thông báo đó đã đọc không?
 (c) Chạm thông báo của đơn đã đóng / đã bị người khác nhận thì mở màn gì?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-NTF-010, SC-NTF-014 + DoD #7 không có oracle cho màn đích</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>a. ver 1.1 lần này ra màn hình theo dõi đơn thôi 
+b. Có đánh dấu đã đọc nhé 
+c. Hiển thị thông báo đơn không tồn tại</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (a) ở v1.1, TẤT CẢ 15 loại thông báo chạm vào đều mở màn 'Theo dõi đơn' (không có bảng màn đích riêng theo từng loại như DoD #7 kỳ vọng — BA đơn giản hoá: v1.1 lần này chỉ ra 'theo dõi đơn' thôi, chưa phân loại theo từng NTF-01..15). (b) chạm 1 thông báo CÓ tự đánh dấu RIÊNG thông báo đó đã đọc (ngoài cơ chế 'đánh dấu tất cả' đã chốt ở C-NTF-03). (c) chạm thông báo của đơn đã đóng/đã bị người khác nhận ⇒ hiển thị thông báo 'đơn không tồn tại' (không mở Theo dõi đơn của đơn đó). CL-NTF-04 ĐÓNG HẲN — SC-NTF-010/014 + DoD #7 có oracle: màn đích thống nhất = 'Theo dõi đơn' cho mọi loại (trừ đơn không tồn tại).
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-NTF-05</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Người nhận thông báo ở vài sự kiện PRD viết mơ hồ: Carrier huỷ nhận (đơn không bị huỷ nhưng NTF-08 là 'Đơn đã bị huỷ bởi…'); giao cho người uỷ quyền/quầy chỉ có NTF-10/11 (không có lời nhắc 'vui lòng xác nhận' như NTF-05) dù người nhận vẫn phải bấm xác nhận.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-25.1.02 (tr.26) · §8.13.1 NTF-05/08/10/11 (tr.47)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(a) Carrier HUỶ NHẬN: người gửi nhận thông báo nào (NTF-08 hay thông báo riêng)? Người nhận có được báo không?
 (b) Giao cho người uỷ quyền / quầy: người nhận có nhận THÊM NTF-05 'vui lòng xác nhận đã nhận hàng' không?
 (c) Người gửi huỷ đơn khi còn 'Chờ ghép': 'các bên còn lại' của NTF-08 = chỉ người nhận?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-NTF-006, SC-NTF-017/018 chưa rõ người nhận; rủi ro đơn kẹt nếu người nhận không được nhắc xác nhận</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. ntf-08 nhé → ngườ nhận có nhé  
+b. có nhé 
+c. đúng nhé </t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (a) Carrier HUỶ NHẬN: người gửi nhận `NTF-08`; người nhận CŨNG được báo (có nhé). (b) giao cho người uỷ quyền/quầy: người nhận có nhận THÊM `NTF-05` 'vui lòng xác nhận đã nhận hàng' (không chỉ NTF-10/11). (c) người gửi huỷ đơn khi còn 'Chờ ghép': 'các bên còn lại' của NTF-08 = CHỈ người nhận (đúng như giả định). CL-NTF-05 ĐÓNG HẲN — SC-NTF-006, SC-NTF-017/018 xác định rõ người nhận thông báo cho cả 3 tình huống.
+— Ghi chú trước đó: 🟡 Trung bình</t>
         </is>
       </c>
     </row>
@@ -1094,159 +1136,159 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>GIFT-qua-cam-on — Quà cảm ơn</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-GIFT-02</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Bấm back (←) từ màn "Tặng quà" (mở từ item mẫu ở tab "Đã hoàn thành") nhảy sang màn "Xác nhận đã nhận hàng" của MỘT ĐƠN KHÁC không liên quan, thay vì quay về "Đơn của tôi". Phát hiện trên item mẫu tĩnh của bản demo nên nhiều khả năng chỉ là giới hạn demo.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-06 KP-01 §6 KB-GIFT-04</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Hiện tượng back-navigation nhảy sai màn này có tái hiện được trên đơn thật ở STG không? Nếu có, đây có phải bug cần fix hay chấp nhận được?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-GIFT-010 yêu cầu Given là đơn thật trên STG (không dùng dữ liệu mẫu) để không kết luận bug sai. Nếu tái hiện với đơn thật, mức độ nghiêm trọng cao hơn đánh giá ban đầu (user có thể thao tác nhầm trên đơn không liên quan, ví dụ xác nhận nhận hàng của đơn khác)</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">-&gt; đây là demo lỗi thôi, quy tăc là back về màn hình trước đó </t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Lỗi của demo. Rule: nút back ở màn 'Tặng quà' quay về MÀN HÌNH TRƯỚC ĐÓ. SC-GIFT-010 assert; STG nhảy sang đơn/màn khác = bug.
 — Ghi chú cũ: Non-blocking cho generate-tc nhưng nên verify sớm trên STG thật</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-GIFT-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-ACT-01 'hoàn thành CHƯA tặng quà thì ra màn Tặng quà' ⇒ ngầm định trạng thái đã/chưa tặng, nhưng PRD không đặc tả vòng đời bước tặng quà.</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>🟡 Partially Resolved — hỏi vòng 2</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-24.1.01 (tr.26) · §8.10 Post-Conditions (tr.43) · §8.12.3 (tr.46) · BA trả lời C-ACT-01</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) Mỗi đơn tặng quà được 1 lần hay nhiều lần?
 (b) Người gửi thoát màn Tặng quà thì vào lại tặng sau được không? Có thời hạn không?
@@ -1254,57 +1296,58 @@
 (d) Chạm NTF-06 'Đơn đã hoàn tất' (vai Người gửi) có mở thẳng màn Tặng quà không?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-GIFT-001/005 (SC-GIFT-005 hiện chỉ dựa quan sát app v1.0)</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a. 1 lần rồi đóng ko cho tặng nữa 
-b. không nhé 
-c. </t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+b. Có nhé, vào lại từ màn hình Hoạt động &gt; tab Đã hoàn thành (nếu chưa tặng se hiên thị chạm để tặng quà, mới đính kèm thêm ui nhé )
+c. UI có mà 
+d. Mở màn tặng quà nhé </t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: (a) mỗi đơn tặng quà ĐÚNG 1 LẦN rồi đóng ⇒ SC-GIFT-005 vế 'không gửi lại được' có nguồn BA. (b) 'không nhé' mơ hồ (không cho tặng sau ⟷ không có thời hạn) và nếu là 'không cho tặng sau' thì mâu thuẫn C-ACT-01. (c)(d) trống ⇒ dòng vòng 2.
 — Ghi chú cũ: 🟢 Thấp</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="220" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="219.75" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-GIFT-04 (vòng 2)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>BA chốt (a) tặng 1 lần rồi đóng. Câu (b) BA trả lời 'không nhé' cho câu gộp 'thoát màn Tặng quà thì vào lại tặng sau được không? Có thời hạn không?' ⇒ 2 cách hiểu. Nếu hiểu 'không cho tặng sau' thì NGƯỢC câu BA ở C-ACT-01 (2026-09-16): 'hoàn thành chưa tặng quà thì ra màn hình tặng quà'. Câu (c)(d) chưa trả lời.</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>🟡 Chờ BA — vòng 2</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-GIFT-04 + C-ACT-01 · DOC-v1.1-01 AC-24.1.01 (tr.26) · §8.12.3 (tr.46) · NTF-06 (tr.47)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(1) Người gửi mở màn Tặng quà rồi thoát KHÔNG gửi — sau đó mở lại đơn có tặng quà được nữa không?
    • Nếu KHÔNG: tap card đơn 'Hoàn thành chưa tặng quà' ở tab Đã hoàn thành (C-ACT-01) mở màn nào?
@@ -1314,21 +1357,29 @@
 (4) Chạm thông báo NTF-06 'Đơn đã hoàn tất' (vai Người gửi) mở Theo dõi đơn hay thẳng màn Tặng quà?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-GIFT-001/005, SC-ACT-009/010 (tap card), SC-NTF-010 chưa assert được nhánh chưa tặng / đã tặng</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình — mâu thuẫn C-ACT-01</t>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.  có nhé, không có thời hạn
+2. Chỉ hiện bạn đã đánh giá thôi + disable (nếu chưa có UI thì vào tìm lại thông tin nhé )
+3. Theo dõi đơn nhé, như 
+4. tặng quà nhé nếu chưa tặng, nếu đã tặng rồi thì ra màn hình theo dõi đơn </t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (1) Người gửi thoát màn 'Tặng quà' KHÔNG gửi rồi vào lại sau VẪN tặng được, KHÔNG có thời hạn ⇒ giải toả mâu thuẫn với C-ACT-01 — 'hoàn thành chưa tặng quà' luôn mở được màn 'Tặng quà' bất kể vào lại lúc nào (khớp câu (a) gốc: mỗi đơn chỉ tặng ĐÚNG 1 LẦN rồi đóng — 'đóng' chỉ tính từ lúc BẤM GỬI tặng, không phải từ lúc thoát màn). (2) Sau khi đã tặng: nút đổi thành 'Bạn đã đánh giá', ở trạng thái DISABLE (không cho bấm lại) — chưa có ảnh UI đính kèm, BA ghi nhận sẽ bổ sung khi có. (3) Tap card đơn Hoàn thành ĐÃ tặng quà (mọi vai) → mở màn 'Theo dõi đơn' (không mở lại màn Tặng quà). (4) Chạm thông báo NTF-06 'Đơn đã hoàn tất' (vai Người gửi): NẾU CHƯA tặng → mở thẳng màn 'Tặng quà'; NẾU ĐÃ tặng → mở màn 'Theo dõi đơn'. Đã thử vibe-check demo 2026-09-17 để đối chứng trực quan nút 'Bạn đã đánh giá' nhưng KHÔNG tới được trạng thái 'Hoàn thành' vì màn 'Xác nhận đã giao' bắt buộc tối thiểu 1 'Ảnh bằng chứng' và ô tải ảnh trong bản demo này không mở được trình chọn file (không phản hồi thao tác click) — bị chặn giữa luồng. Không ảnh hưởng tới việc đóng CL vì BA đã trả lời đầy đủ bằng lời cho cả 4 câu. CL-GIFT-04 ĐÓNG theo câu trả lời BA; ảnh UI 'Bạn đã đánh giá' xin bổ sung khi có (theo dõi ở GIFT CHANGELOG nếu cần).
+— Ghi chú trước đó: 🟡 Trung bình — mâu thuẫn C-ACT-01</t>
         </is>
       </c>
     </row>
@@ -1352,146 +1403,146 @@
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>FEED-bang-tin — Bảng tin &amp; Chi tiết tin (v1.0, không có delta v1.1)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-FEED-01</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Gộp 2 câu hỏi cùng bề mặt Bảng tin/Chi tiết tin: (a) nút "Tôi mang giúp được" xuất hiện trên card ở Bảng tin hay chỉ ở màn Chi tiết tin? (b) bản chính thức có tích hợp bản đồ thật (GPS/Google Maps) hay giữ placeholder?</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D1b US-D07 L176 vs DOC-v1.0-02 §3.3 đoạn 3 · §7 dòng 10</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Nút CTA "Tôi mang giúp được" có trên card ở Bảng tin, hay chỉ xuất hiện khi vào màn Chi tiết tin?
 (b) Bản chính thức có tích hợp bản đồ thật (GPS/Google Maps) không, hay vẫn giữ placeholder tĩnh?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-FEED-002 đã cố ý không assert CTA trên card; SC-FEED-009 chỉ assert trạng thái hiện tại. Ảnh hưởng completeness của TC card + số bước luồng ghép</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>a, chỉ xuất hiện ở chi tiết tin 
 b. có hiển thị được map nhé (sẽ có vài case không hiển thị được map cho data văn phòng bị thiếu location ) → khi test sẽ được cung cấp file data</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: (a) Nút 'Tôi mang giúp được' CHỈ ở Chi tiết tin (PRD AC-12.1.01 'tại thẻ tin hoặc chi tiết' là PRD chưa cập nhật). (b) CÓ bản đồ thật ⇒ SC-FEED-009 đảo từ 'placeholder tĩnh' sang 'bản đồ thật'; văn phòng thiếu location thì không hiện map → C-FEED-02 + xin file data.
 — Ghi chú cũ: Module FEED không có delta ở v1.1 (PRD không đụng tới) — CL này kế thừa nguyên trạng từ v1.0</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-FEED-02</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>BA: 'vài case không hiển thị được map cho data văn phòng bị thiếu location → khi test sẽ cung cấp file data' — chưa nói UI hiển thị gì thay thế.</t>
         </is>
@@ -1501,12 +1552,12 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-FEED-01(b) · DOC-v1.0-02 §3.4 (khung 'Bản đồ · ~X km')</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) Văn phòng thiếu location: ẩn hẳn khung bản đồ, hiện placeholder + thông báo, hay map chỉ 1 điểm?
 (b) Dòng '~X km' tính theo toạ độ nào; thiếu location thì ẩn hay hiện '—'?
@@ -1514,17 +1565,17 @@
 (d) Xin file data văn phòng thiếu location trước khi viết TC.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-FEED-009 chỉ assert được nhánh có location</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a, hiển placehoder + thông báo (nhưng case này do data sai thôi có thể ko cần viết tc đâu)
 b. thiếu thì hiện 0km , tính từ điểm nhận đến điểm giao
@@ -1532,12 +1583,12 @@
 d. cung cấp r nhé </t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: (a) thiếu location ⇒ placeholder + thông báo (BA: lỗi data, có thể không viết TC → SC-FEED-015 P3) · (b) km tính điểm nhận → điểm giao; thiếu ⇒ '0km' · (c) ảnh tĩnh có vẽ tuyến (không test zoom/pan) · (d) đã nhận file. SC-FEED-009 sửa Then. Dữ liệu toạ độ trong file lỗi diện rộng ⇒ C-FEED-05.
 — Ghi chú cũ: CẬP NHẬT 2026-09-16: ĐÃ NHẬN file data location_address_catalog.xlsx (399 văn phòng, DOC-v1.1-04) ⇒ câu (d) xong. ⚠️ Cả 399 dòng coordinate_status = MISSING; 61 dòng thiếu lat/lng; 34 dòng toạ độ nằm ngoài Việt Nam (vd 51.93, -8.62) — hỏi thêm BA: toạ độ bản đồ lấy từ đâu nếu file thiếu/sai?
@@ -1545,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-FEED-03</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>PRD nói Bảng tin có 'cả hai tab' (EMP-04) và 'lọc/tìm kiếm' (§7.1), AC-20.1.01 nói 'bất kỳ tab nào của bảng tin' — nhưng không đặc tả gì; demo chỉ thấy 1 danh sách.</t>
         </is>
@@ -1561,54 +1612,54 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 EMP-04 (tr.51) · §7.1 (tr.30) · AC-20.1.01 (tr.24)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(a) 2 tab của Bảng tin là gì?
 (b) Có ô tìm kiếm / bộ lọc nào (khu vực, ngày, loại hàng…)?
 (c) 'Gợi ý mở rộng khu vực' ở empty state là nút bấm hay chỉ là câu chữ?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Theo Custom Rule §10.2 mỗi tab cần ≥1 SC riêng — hiện chưa có; SC-FEED-001/013</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a. Chỉ có 1 dánh danh đâu có tab gì 
 b. không có gì như demo đang đúng r
 c. </t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: Bảng tin = 1 danh sách, KHÔNG tab, KHÔNG lọc/tìm kiếm (như demo) ⇒ Custom Rule §10.2 không áp; SC-FEED-013 bỏ 'cả hai tab'. PRD EMP-04/§7.1/AC-20.1.01 chưa cập nhật ⇒ dòng đề nghị cập nhật PRD. Câu (c) 'gợi ý mở rộng khu vực' BA để trống ⇒ gộp hỏi ở C-HOME-04 (vòng 2).
 — Ghi chú cũ: 🟡 Trung bình</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="120" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="7" ht="120" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-FEED-04</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>AC-13.1.02 liệt kê thông tin trước khi ghép gồm 'phòng ban người gửi' (không có họ tên) và 'điểm lấy/giao'; BR03-03 nói họ tên chỉ lộ SAU ghép; NFR-10 nói ĐỊA CHỈ chỉ trả cho 2 người trong cặp ghép. Demo hiện tên người gửi + nút gọi trước ghép.</t>
         </is>
@@ -1618,68 +1669,68 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-13.1.02 (tr.21) · BR03-03 (tr.36) · NFR-10 (tr.54) · ảnh FEED_02</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Trước khi ghép, màn Chi tiết tin:
 (a) có hiện HỌ TÊN người gửi không? Tên người nhận?
 (b) hiện địa chỉ lấy/giao ĐẦY ĐỦ hay chỉ rút gọn (quận / toà nhà)?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SC-FEED-007, SC-FEED-010 (P1 — bảo mật thông tin trước ghép) chưa rõ phạm vi</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a, chỉ ẩn sdt thôi mà ?? đâu có rule ẩn tên 
 b. hiên thị theo data đã gởi </t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: Trước ghép CHỈ ẩn SĐT (+ nút Gọi); họ tên hiện; địa chỉ lấy/giao hiện đầy đủ theo data đã đăng. SC-FEED-007 thêm assert tên; SC-FEED-010 giữ nguyên (P1). Không log bug vì tên/địa chỉ hiện trước ghép. PRD BR03-03/NFR-10 ghi ngược ⇒ dòng đề nghị cập nhật PRD.
 — Ghi chú cũ: 🔴 Cao — liên quan bảo mật</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="200" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="8" ht="199.5" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-FEED-05</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>File location_address_catalog.xlsx BA cấp (399 văn phòng): cả 399/399 dòng coordinate_status = MISSING; 61 dòng không có lat/lng; 34 dòng lat/lng nằm ngoài Việt Nam (vd 51.93, -8.62). Nếu app lấy toạ độ từ file này thì hầu hết tin sẽ rơi vào nhánh placeholder / '0km'.</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-04 location_address_catalog.xlsx · BA trả lời C-FEED-02 (2026-09-17)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>(a) Bản đồ và '~X km' lấy toạ độ từ đâu: cột lat/lng của file này, geocode từ địa chỉ, hay DB khác? coordinate_status = MISSING nghĩa là gì?
 (b) 34 dòng toạ độ ngoài Việt Nam: app vẽ theo toạ độ đó (sai vị trí) hay coi là thiếu toạ độ?
@@ -1687,46 +1738,54 @@
 (d) Xin 2 cặp văn phòng mẫu trên STG: 1 cặp đủ toạ độ đúng (hiện bản đồ) · 1 cặp thiếu toạ độ.</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-FEED-009 (bản đồ thật) không dựng được Given; SC-FEED-015 chưa có câu thông báo</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình — chặn Given SC-FEED-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="200" customHeight="1" s="12">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>a: từ cột lat/lng trên file (file này được dev import và db), coordinate_status bỏ qua đừng quan tâm, chưa dùng đến nhé 
+b. nếu có đầy đủ data lat/lng là có load lên, thiếu 1 trong 2 là do stag data sai thôi (ưu tiên test có đây đủ ), còn trường hợp tọa đồ ngoài  việt nam thì bỏ qua (cũng do data sai )
+c. đúng r, nhưng này do data stag sai(có thể bỏ qua, ưu tiên các case đầy đủ data)
+d. lấy từ file đi, các dòng có đầ đủ cả 2  lat/lng là được</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (a) bản đồ/'~X km' lấy toạ độ từ đúng cột lat/lng của file `location_address_catalog.xlsx` (đã import vào DB) — cột `coordinate_status` KHÔNG dùng tới, bỏ qua hoàn toàn. (b) văn phòng có ĐẦY ĐỦ lat/lng cả 2 điểm (lấy + giao) ⇒ hiện bản đồ thật; thiếu 1 trong 2 là DO DATA STG SAI (không phải bug app) — ưu tiên viết TC cho case đủ data, case thiếu data có thể bỏ qua/P3. (c) toạ độ 34 dòng ngoài Việt Nam cũng là DATA SAI ⇒ BỎ QUA case này, không cần viết TC riêng. (d) dùng đúng file đã cấp `location_address_catalog.xlsx`, CHỌN CÁC DÒNG CÓ ĐẦY ĐỦ CẢ 2 lat/lng làm test data cho case tích cực. CL-FEED-05 ĐÓNG HẲN — SC-FEED-009 dựng được Given với dữ liệu văn phòng đủ toạ độ; SC-FEED-015 (thiếu toạ độ) hạ xuống P3/optional vì bản chất là data lỗi diện rộng, không phải rule nghiệp vụ cần test kỹ.
+— Ghi chú trước đó: 🟡 Trung bình — chặn Given SC-FEED-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="199.5" customHeight="1" s="15">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>— (đề nghị BA cập nhật PRD)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Các rule BA đã trả lời cho Bảng tin / Chi tiết tin nhưng PRD v1.1 ghi khác — cần BA cập nhật PRD để dev làm đúng.</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>🟡 Chờ BA cập nhật PRD</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-12.1.01 (tr.20) · AC-13.1.02 (tr.21) · AC-20.1.01 (tr.24) · §7.1 (tr.30) · BR03-03 (tr.36) · EMP-04 (tr.51) · NFR-10 (tr.54)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(1) Nút 'Tôi mang giúp được' CHỈ ở Chi tiết tin (AC-12.1.01 ghi 'tại thẻ tin hoặc màn chi tiết tin').
 (2) Bảng tin 1 danh sách, không tab, không lọc/tìm kiếm (EMP-04 'cả hai tab', §7.1 'lọc/tìm kiếm', AC-20.1.01 'không tìm được').
@@ -1735,19 +1794,23 @@
 BA cập nhật PRD theo các rule trên?</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Không chặn generate-tc (TC viết theo BA). Dev đọc PRD cũ có thể ẩn tên/địa chỉ trước ghép (NFR-10 kiểm ở server) ⇒ SC-FEED-007 FAIL dù dev cho là đúng.</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>Đúng r, BA sẽ cập nhật lại tài liệu cho các mục trên</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>🟢 Thấp — không chặn</t>
         </is>
@@ -1770,320 +1833,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col hidden="1" width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col hidden="1" width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col hidden="1" width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col hidden="1" width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>ORD-dang-tin — Đăng tin &amp; Quản lý tin</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-17 — ORD HẾT điểm hỏi BA (16/16 CL Resolved, C-ORD-18 đóng ngày 2026-09-17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-ORD-04</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>PRD TỰ MÂU THUẪN (không phải 2 tài liệu khác nhau): §8.1.4 liệt kê "Thuốc/Y tế" là 1 trong 8 giá trị hợp lệ của "Loại hàng"; nhưng BR01-07 (cách đó 1 trang, cùng FR01) xếp "thuốc" vào nhóm hàng cấm không được đăng.</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>🟡 Partially Resolved — hỏi vòng 2</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.4 UI/Field Spec (tr.35) vs §8.1.1 BR01-07 (tr.34)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Chip "Thuốc/Y tế" có phải là sót của field spec (cần bỏ khỏi danh mục chọn), hay
 (b) BR01-07 chỉ nhắm thuốc kê đơn/chất gây nghiện, còn "Thuốc/Y tế" thông thường vẫn được đăng?
 (c) Nếu là (b): app chặn ở bước nào — ngay lúc chọn chip, hay chỉ cảnh báo qua banner như v1.0?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-ORD-031..035 phải GHI NHẬN hành vi thật của app, không được assert chiều nào cho tới khi chốt — viết TC sai chiều sẽ tạo bug report giả</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a. Thuốc/Y tế  có nhé 
-B, c. không giới hạn hay thông bao gì, hiện tại có thể đăng bất kỳ 
+B, c. không giới hạn hay thông bao gì, hiện tại có thể đăng bất kỳ , ver này không cấm gì nhé, đăng bất kỳ đều dược và không giới hạn và thông có bao gì
 </t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Chip 'Thuốc/Y tế' GIỮ; chọn chip KHÔNG chặn, KHÔNG cảnh báo → SC-ORD-031..035 phần chip assert được. Còn treo nửa câu BR01-07 'hàng cấm không được đăng' → xem dòng vòng 2.
 — Ghi chú cũ: 🔴 Ưu tiên hỏi đầu tiên — cả 2 vế mâu thuẫn đều là DOC-v1.1-01 nên không thể áp thứ tự ưu tiên nguồn để tự phân xử</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="90" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-ORD-13</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Đăng tin có tra "Danh bạ nội bộ" theo email công ty người nhận để tự điền tên/SĐT/địa chỉ. Chưa biết STG đã nối dữ liệu thật hay đang mock, và chưa có email mẫu để test nhánh "không tìm thấy".</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>🟡 Partially Resolved — hỏi vòng 2</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.1 BR01-09 (tr.34) · §4 SCOPES (tr.9)</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) STG đã nối Danh bạ nội bộ thật chưa, hay đang dùng mock?
 (b) Xin 2 email mẫu: 1 email CÓ trong danh bạ, 1 email đúng tên miền nội bộ nhưng KHÔNG có trong danh bạ.
 (c) Tên miền nội bộ hợp lệ là những tên miền nào (để test nhánh "ngoài tên miền")?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-ORD-058/059/060 (1 cái P1) không seed được tiền đề nếu thiếu (b) → verdict BLOCKED. Email tự chế không thay thế được vì không phân biệt được "không tìm thấy" với "tích hợp hỏng"</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>QTHT/Dev</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>a. là thông tin trên app hris, thông tin phỉa có trên hris, và trạng thái là đang làm việc</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>a. là thông tin trên app hris, thông tin phỉa có trên hris, và trạng thái là đang làm việc
+B: stag_giangdc2@fpt.com  có, abctesst@fpt.com” không có (Có thì dùng accout lúc test sẽ cung cấp sau ) 
+c. VD: @fpt.vn, @gmail.com</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Nguồn = HRIS; chỉ tra thấy nhân sự ĐANG LÀM VIỆC (rule mới → thêm nhánh 'đã nghỉ việc'). Câu (b) email mẫu và (c) tên miền BA chưa trả lời → dòng vòng 2.
-— Ghi chú cũ: Xin xác nhận TRƯỚC generate-tc, đừng để tới lúc execute mới phát hiện không seed được</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+— Ghi chú cũ: Xin xác nhận TRƯỚC generate-tc, đừng để tới lúc execute mới phát hiện không seed được
+⛔ ĐÍNH CHÍNH 2026-09-17 (QC GiangDC2): (3) tên miền hợp lệ là EMAIL CÔNG TY "@fpt.com" — vế "@fpt.vn, @gmail.com" HẾT HIỆU LỰC; "@gmail.com" nay là DỮ LIỆU INVALID của SC-ORD-060 (nhánh ngoài tên miền), "@fpt.vn" chưa xác nhận lại ⇒ không dùng. (4) vế "email đã nghỉ việc ⇒ nhập thủ công, KHÔNG chặn đăng tin" HẾT HIỆU LỰC — C-ORD-14 (mới hơn) chốt nút "Tiếp theo" DISABLE, không cho tạo đơn, áp cho cả 2 case (không tồn tại · đã nghỉ việc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-ORD-09</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Danh mục "Loại hàng" nay đã thống nhất còn 1 danh mục PRD với 8 giá trị (đã hết mơ hồ "3 nguồn 3 danh mục" của v1.0). Nhưng app STG hiện nhãn đầu là "Giấy tờ, hồ sơ", PRD ghi "Tài liệu" — lệch doc ⟷ app ở đúng 1 nhãn xuất hiện trong Steps của rất nhiều TC.</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.4 UI/Field Spec, dòng "Loại hàng" (tr.35)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Nhãn nào là chuẩn để dùng trong TC — "Tài liệu" (PRD) hay "Giấy tờ, hồ sơ" (app hiện tại)? Nếu PRD chuẩn thì đây là defect UI cần dev sửa; nếu app chuẩn thì PRD cần đính chính.</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>⛔ Ràng buộc đang áp dụng: TC dùng nhãn theo app STG, TUYỆT ĐỐI không dùng "Tài liệu" cho tới khi CL này được chốt (03_test-cases/v1.0/CHANGELOG.md §2)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Tài liệu </t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Nhãn chuẩn = 'Tài liệu' (theo PRD). App STG còn hiện 'Giấy tờ, hồ sơ' ⇒ defect UI, log bug. Ràng buộc 'không dùng nhãn Tài liệu' HẾT HIỆU LỰC. (Ngược với C-ACT-02 — BA quyết từng nhãn.)
 — Ghi chú cũ: Nên gộp 1 lượt hỏi BA cùng C-ACT-02 (nhãn 2 tab) vì cùng bản chất doc ⟷ app, cùng là lỗi #1 của đợt phân tích cũ</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="120" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="7" ht="120" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-ORD-04 (vòng 2)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>BA trả lời 'không giới hạn hay thông báo gì, hiện tại có thể đăng bất kỳ' — rộng hơn câu hỏi. PRD BR01-07 vẫn còn câu 'Hàng cấm (thuốc, vũ khí, chất nguy hiểm, hàng phi pháp) không được đăng'; v1.0 có banner thông tin hàng cấm; NFR-13 đòi lưu phiên bản điều khoản.</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>🟡 Chờ BA — vòng 2</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.1 BR01-07 (tr.34) · §9 NFR-13 (tr.54)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>(1) Câu 'hàng cấm … không được đăng' của BR01-07 bỏ hẳn khỏi PRD, hay chỉ còn là cam kết trong nội dung điều khoản người dùng tick?
 (2) Banner thông tin hàng cấm ở wizard (v1.0) còn hiển thị không?
 (3) Nội dung điều khoản miễn trừ có đoạn nào về hàng cấm để test verbatim không? Có hiển thị phiên bản điều khoản không?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SC-ORD-031..035 phần banner/điều khoản vẫn chỉ ghi nhận, chưa assert</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình — non-blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. ver hiện tại chưa làm, có thê làm trong tương lai nên tạm thời vẫn để v, nhưng bỏ qua nhé 
+2. không nhé 
+3. không </t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (1) app hiện tại CHƯA làm banner/cảnh báo hàng cấm — có thể làm trong tương lai, TẠM BỎ QUA ở v1.1 (không viết SC assert banner). (2) banner thông tin hàng cấm ở wizard (v1.0) KHÔNG còn hiển thị ở v1.1. (3) KHÔNG có nội dung điều khoản nào về hàng cấm để test verbatim. CL-ORD-04 ĐÓNG HẲN (gộp cùng vòng 1: chip 'Thuốc/Y tế' giữ, không chặn/không cảnh báo).
+— Ghi chú trước đó: 🟡 Trung bình — non-blocking</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-ORD-13 (vòng 2)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Đã biết nguồn = HRIS, chỉ nhân sự đang làm việc. Chưa có dữ liệu test và chưa rõ hành vi nhánh 'đã nghỉ việc'.</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>🟡 Chờ BA — vòng 2</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.1 BR01-09 (tr.34) · AC-04.1.01/04.1.02/04.2.01 (tr.17)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>(1) STG đang nối HRIS thật hay HRIS môi trường test/mock?
 (2) Xin email mẫu 3 loại: đang làm việc (dùng stag_anhdc4@fpt.com được không?) · đã nghỉ việc · đúng tên miền nhưng không có trên HRIS.
@@ -2092,205 +2165,352 @@
 (5) Hồ sơ HRIS thiếu SĐT/địa chỉ thì tự điền phần có, bỏ trống phần thiếu?</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-ORD-058/059/060 (1 P1) BLOCKED nếu thiếu (2); nhánh nghỉ việc chưa có SC</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA/QTHT/Dev</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — chặn generate-tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1" s="12">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. môi trường stag
+2. stag_anhdc4@fpt.com được, đã nghĩ việc điền đại thông ví dụ đi, khi vibe test t sẽ cung cấp dữ liệu đúng 
+3.  @fpt.vn, @gmail.com
+4. không tìm thấy thôi, không báo gì 
+5. đúng nhé  </t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (1) STG dùng môi trường stag (không phải HRIS thật production). (2) email mẫu 'đang làm việc' = stag_anhdc4@fpt.com dùng được; nhánh 'đã nghỉ việc' BA sẽ cấp dữ liệu thật lúc vibe-test (dùng placeholder tạm khi generate-tc). (3) tên miền nội bộ hợp lệ: @fpt.vn, @gmail.com. (4) email đã nghỉ việc ⇒ xử lý giống 'Không tìm thấy · nhập thủ công', KHÔNG báo lỗi riêng, KHÔNG chặn đăng tin. (5) hồ sơ HRIS thiếu SĐT/địa chỉ ⇒ tự điền phần có, bỏ trống phần thiếu (đã chốt vòng 1, BA reconfirm). CL-ORD-13 ĐÓNG — hết blocking cho generate-tc; chỉ còn nợ nhỏ 'email mẫu thật cho case đã nghỉ việc' sẽ cấp lúc vibe-test (không chặn viết TC, dùng placeholder).
+— Ghi chú trước đó: 🔴 Cao — chặn generate-tc
+⛔ ĐÍNH CHÍNH 2026-09-17 (QC GiangDC2): (3) tên miền hợp lệ là EMAIL CÔNG TY "@fpt.com" — vế "@fpt.vn, @gmail.com" HẾT HIỆU LỰC; "@gmail.com" nay là DỮ LIỆU INVALID của SC-ORD-060 (nhánh ngoài tên miền), "@fpt.vn" chưa xác nhận lại ⇒ không dùng. (4) vế "email đã nghỉ việc ⇒ nhập thủ công, KHÔNG chặn đăng tin" HẾT HIỆU LỰC — C-ORD-14 (mới hơn) chốt nút "Tiếp theo" DISABLE, không cho tạo đơn, áp cho cả 2 case (không tồn tại · đã nghỉ việc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1" s="15">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>C-ORD-14</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Email người nhận không tra thấy (không có trên HRIS / đã nghỉ việc) vẫn cho đăng tin bằng thông tin nhập tay ⇒ người nhận KHÔNG có tài khoản ⇒ không ai bấm được 'Xác nhận đã nhận hàng' (BR10-01 chỉ người nhận) ⇒ đơn kẹt ở 'Đã giao'. PRD cũng không cấm người nhận = người gửi hoặc = người vận chuyển.</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-04.1.02 (tr.17) · BR10-01 (tr.43) · BR03-04 (tr.36)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(a) Người nhận nhập tay (không có tài khoản) thì đơn được đóng bằng cách nào?
 (b) Người gửi có được nhập chính email của mình làm người nhận không?
 (c) Người nhận của đơn có được bấm 'Tôi mang giúp được' cho chính đơn đó không?</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Có thể sinh đơn kẹt vĩnh viễn (không có tool admin — C-CNL-03). SC-ORD-059, SC-FEED-012 chưa rõ kết quả mong đợi</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — rủi ro đơn kẹt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1" s="12">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>a. đúng tên chọn được mới cho tạo đơn (không được thì disable btn Tiếp theo )
+b. Không 
+c. không nhé, (chỗ nay thao tác demo để rõ hơn )</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16, đóng 2026-09-17 sau vibe-check: (a) người nhận nhập tay không tra được HRIS ⇒ KHÔNG cho tạo đơn (nút 'Tiếp theo' bị disable) — vậy nhánh 'đơn kẹt vĩnh viễn' KHÔNG xảy ra vì app chặn ngay từ bước tạo đơn. (b) người gửi KHÔNG được nhập chính email mình làm người nhận. (c) người nhận của đơn KHÔNG được bấm 'Tôi mang giúp được' cho chính đơn đó. Đã thử xác minh lại (c) qua vibe-check demo 2026-09-17 nhưng do demo dùng chung 1 'đơn' toàn cục cho cả 3 vai (xem C-ASN-03) nên không dựng được kịch bản sạch 'người nhận xem đúng tin của chính mình trong Bảng tin' để so trực quan — không mâu thuẫn với câu trả lời BA, chỉ là demo không đủ dữ liệu để đối chứng thêm. CL-ORD-14 ĐÓNG theo câu trả lời BA.
+— Ghi chú trước đó: 🔴 Cao — rủi ro đơn kẹt
+⚠️ 2026-09-17: câu trả lời này ĐẢO PRD BR01-09/AC-04.1.02 ("không thấy thì cho nhập thủ công") và đảo luôn C-ORD-13(4). SC-ORD-059 đã sửa Then (NEW → MODIFIED): nút "Tiếp theo" disable, KHÔNG mở 3 ô nhập tay. Đề nghị BA cập nhật PRD cho khớp. Khi chạy TC lấy câu trả lời BA — STG cho nhập tay và tạo được đơn ⇒ LOG BUG, không sửa oracle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1" s="15">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>C-ORD-15</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>3 biên thời gian PRD không định nghĩa: cách tính 'tối đa 7 ngày'; buổi đã trôi qua trong ngày hôm nay; thời điểm chính xác đơn chuyển 'Hết hạn'.</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR01-04 (tr.34) · §8.1.4 Buổi mong muốn (tr.36) · BR05-03 (tr.38) · BR09-04 (tr.42)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>(a) 'Tối đa 7 ngày' tính GỒM ngày đầu (Từ 15 → Đến tối đa 21) hay cộng 7 (→ 22)? Áp giống cho tuyến OFFER và lịch hẹn cầm hàng về?
 (b) Đăng tin sau 19:00 với mặc định 'hôm nay + Sau giờ làm' (đã qua): app chặn, tự dời ngày, hay cho đăng?
 (c) 'Hết ngày cuối' = 00:00 ngày kế tiếp, hay theo job chạy định kỳ (bao lâu 1 lần)?</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>SC-ORD-028 (boundary), SC-ORD-045 (EXPIRED) không chốt được giá trị biên / thời điểm kết luận</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1" s="12">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>a đến 22 nhé 
+b. chặn nhé, ví dụ đăng tin sau 12h thì không cho chọn Sáng 
+c. chạy job cuối ngày</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (a) 'tối đa 7 ngày' = Từ ngày X → Đến tối đa ngày X+7 (vd Từ 15 → Đến 22), áp dụng chung cho tuyến OFFER và lịch hẹn cầm hàng về. (b) đăng tin sau 12h thì KHÔNG cho chọn buổi 'Sáng' của ngày hôm đó (app CHẶN, không tự dời ngày, không cho đăng buổi đã qua). (c) mốc chuyển 'Hết hạn' chạy theo JOB CUỐI NGÀY (không phải 00:00 tức thời). CL-ORD-15 ĐÓNG theo câu trả lời BA — không cần verify thêm qua demo (thuộc logic backend/thời gian, demo tĩnh không mô phỏng được).
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1" s="15">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>C-ORD-16</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>AC-08.1.01 chỉ minh hoạ 'đổi địa chỉ giao'. Không nói sửa được field nào và hệ quả khi sửa. Ma trận quyền cho chủ tin OFFER sửa tin nhưng không có đặc tả vòng đời tin OFFER.</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 (demo không hỗ trợ câu c) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-08.1.01 (tr.19) · BR05-02 (tr.38) · §7.3 ma trận quyền (tr.32) · AC-19.1.01/20.1.01 (tr.23-24)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>(a) Khi đơn 'Chờ ghép', sửa được những field nào (ảnh, email người nhận, khoảng ngày/buổi, người uỷ quyền…)? Sửa email có tra lại HRIS?
 (b) Sửa khoảng ngày có tính lại mốc Hết hạn? Sửa điểm lấy/giao có chạy lại khớp tuyến + bắn lại thông báo? Người nhận có được báo khi đơn bị sửa?
 (c) Tin OFFER: sửa ở đâu, huỷ được không, có tự hết hạn không, hiển thị ở 'Đơn của tôi' với nhãn trạng thái gì?</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>SC-ORD-043 chỉ test được 1 field; SC-ORD-041 và luồng OFFER không có vòng đời để test</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1" s="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. sửa được tất cả như tạo mới, rule check lại như tạo mới luôn nha
+b. ngày không check check lại(Ví dụ đang chọn buổi sáng→ chiều sửa vẫn đc ko báo lỗi )
+c. Kiểm tra lại demo giúp t nhé </t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): đã thử đăng tin OFFER ('Tôi nhận giao hàng') trên demo để kiểm tra câu (c) 'tin OFFER hiển thị ở Đơn của tôi với nhãn trạng thái gì'. PHÁT HIỆN GIỚI HẠN DEMO giống hệt C-ASN-03: bản demo dùng chung 1 'đơn' toàn cục cho cả 3 vai — đăng OFFER KHÔNG tạo bản ghi độc lập mà GHI ĐÈ trực tiếp lên đơn NEED đang có (địa chỉ giao hàng của đơn cũ bị thay bằng điểm đến vừa nhập cho tuyến OFFER); bấm 'Theo dõi đơn' từ màn xác nhận OFFER dẫn thẳng về ĐÚNG đơn NEED đó, không có card/tin OFFER riêng nào xuất hiện thêm ở 'Đơn của tôi'. ⇒ KHÔNG THỂ verify câu (c) qua demo này — cần BA mô tả bằng lời hoặc ảnh chụp UI thật (STG/Figma) thay vì thao tác demo.
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1" s="15">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>C-ORD-17</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>PRD hứa 'gỡ hoặc đăng lại' tin hết hạn (AC-09.1.01, NTF-09, §8.12.3) nhưng không đặc tả. Rule v1.0: card 'Hết hạn' KHÔNG tap được.</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-09.1.01 (tr.19) · §8.13.1 NTF-09 (tr.47) · §8.12.3 (tr.46)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>(a) 'Gỡ' là nút gì, làm gì (xoá khỏi Đơn của tôi? — mâu thuẫn 'đơn đóng là bất biến')?
 (b) 'Đăng lại' mở wizard nạp sẵn dữ liệu cũ (kể cả ảnh) hay wizard trắng?
 (c) Card 'Hết hạn' có mở được để 'Xem lý do · đăng lại' không?</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>SC-ORD-045, SC-ACT-009 (card Hết hạn không tap được) có thể sai</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Thấp</t>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. Cái thông báo câu từ bị dư thôi, không có chức năng gỡ
+b. Đăng lại là luồng đăng mới tin (chon lại thông tin từ đầu)
+c. Hiển thị tab đã hoàn thành,label  hết hạn (demo có ) </t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (a) chữ 'gỡ hoặc đăng lại' trong PRD là câu dư do soạn thảo — app KHÔNG có chức năng 'gỡ' tin, đề nghị BA sửa PRD bỏ chữ 'gỡ'. (b) 'Đăng lại' = mở luồng ĐĂNG TIN MỚI, chọn lại toàn bộ thông tin từ đầu (không nạp sẵn dữ liệu cũ). (c) tin hết hạn hiển thị ở tab 'Đã hoàn thành' với nhãn trạng thái 'Hết hạn' (label này BA xác nhận có trên demo) — card MỞ được để xem lý do, không giữ rule v1.0 'không tap được'. CL-ORD-17 ĐÓNG theo câu trả lời BA (BA tự xác nhận demo đã thể hiện đúng label 'Hết hạn' ở tab 'Đã hoàn thành' — QA chưa tự tay đối chứng lại card này trong lượt vibe-check 2026-09-17, đơn demo dùng để test hôm nay chưa từng đạt trạng thái Hết hạn).
+— Ghi chú trước đó: 🟢 Thấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="109.5" customHeight="1" s="15">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>C-ORD-16 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Câu (c) duy nhất còn lại: tin OFFER (tuyến đường) hiển thị ở màn "Đơn của tôi" ra sao — demo không dựng được vì dùng chung 1 đơn toàn cục, đăng OFFER ghi đè lên đơn NEED thay vì tạo card riêng.</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved — QA tự verify qua demo 2026-09-17, không cần BA trả lời</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 AC-19.1.01/AC-20.1.01 (tr.23-24) · ảnh 00_input/v1.1/design/ORD_08_dangtin_offer_ghide_len_don_dang_co.png (bằng chứng giới hạn demo)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>Tin OFFER (tuyến đường bạn đăng ở "Tôi nhận giao hàng") hiện ở "Đơn của tôi" như thế nào: có card riêng không, card trông ra sao (thông tin gì), nhãn trạng thái ghi gì, tap vào mở màn nào? Xin gửi ảnh chụp màn hình thật (STG hoặc Figma) vì demo hiện tại không dựng được tin OFFER độc lập để chụp.</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>SC-ORD-041, SC-ACT-015 (card + nhãn tin OFFER) chưa viết được Then chính xác</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>BA/PM</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">đã bổ sung ui ORD_08_card toi nhan giao hang, card sẽ ntn nhé </t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>Duy nhất 1 câu còn lại của C-ORD-16 — các câu (a)(b) đã Resolved 2026-09-16.
+⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2): ORD-dang-tin/risk_assessment.md · C-ORD-16 ĐÓNG HẲN 2026-09-17 — giải qua kết quả C-ACT-04 (cùng câu hỏi, khác module): đã tự verify qua demo (tab Hoạt động → Đang diễn ra), thấy được card OFFER. Không cần trả lời thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1" s="15">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>C-ORD-18</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Ảnh UI thật wizard Bước 1/3 "Thông tin hàng" (QC cung cấp 2026-09-17) lệch PRD §8.1.4 ở 4 điểm: (1) "GIÁ TRỊ HÀNG (ƯỚC TÍNH)" có MỐC TIỀN (Dưới 1 triệu đ / 1–5 triệu đ / Trên 5 triệu đ) — không nguồn nào từng có con số; (2) nhãn UI "TRỌNG LƯỢNG" ⟷ PRD "Khối lượng", option thêm nhãn phụ Nhẹ/Trung bình/Nặng; (3) kiểu control là 3 CHIP ⟷ PRD ghi Dropdown; (4) block Ghi chú nằm TRÊN CÙNG, trước "Thông tin hàng".</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 §8.1.4 UI/Field Spec (tr.35) · §8.1.1 BR01-02/BR01-03 (tr.34) ⟷ DOC-v1.1-03 ảnh "gia tri hang uoc tinh.png" (demo)</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>(a) 3 mốc tiền (Dưới 1 triệu đ / 1–5 triệu đ / Trên 5 triệu đ) có phải con số CHÍNH THỨC không? Nếu có, đề nghị bổ sung vào §8.1.4 để QC assert cứng.
+(b) Nhãn chính thức là "Trọng lượng" hay "Khối lượng"? Có giữ nhãn phụ Nhẹ/Trung bình/Nặng không?
+(c) 3 trường Giá trị hàng / Trọng lượng / Kích thước là CHIP (theo UI) hay DROPDOWN (theo PRD)? PRD cần sửa?
+(d) Ghi chú đặt TRƯỚC block "Thông tin hàng" có đúng thiết kế không?</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>SC-ORD-008/009/010 (Giá trị hàng) · SC-ORD-011 (Ghi chú) · SC-ORD-052/053 (Trọng lượng/Kích thước) — chưa assert được nhãn + mốc tiền</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>a. chính thức nhé
+b. Trọng lượng, Có giữ nhãn phụ Nhẹ/Trung bình/Nặng
+c. Theo UI nhé , lấy Ui làm chuẩn
+d. đúng đây là textbox cho phép nhập nhé</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17 — C-ORD-18 ĐÓNG HẲN: (a) 3 mốc tiền là CON SỐ CHÍNH THỨC ⇒ SC-ORD-008/009/010 assert cứng 'Dưới 1 triệu đ' / '1 – 5 triệu đ' / 'Trên 5 triệu đ'; PRD §8.1.4 THIẾU thông tin này, đề nghị BA bổ sung. (b) Nhãn chính thức 'Trọng lượng' (PRD ghi 'Khối lượng' HẾT HIỆU LỰC), GIỮ nhãn phụ Nhẹ/Trung bình/Nặng ⇒ SC-ORD-052 assert cứng 3 chip 'Dưới 5 kg (Nhẹ)' / '5 – 10 kg (Trung bình)' / 'Trên 10 kg (Nặng)'. (c) LẤY UI LÀM CHUẨN ⇒ cả 3 trường là CHIP nằm ngang, PRD ghi 'Dropdown' HẾT HIỆU LỰC; Steps của TC viết 'nhấn chip', KHÔNG viết 'mở dropdown'. (d) Block Ghi chú đặt TRÊN 'Thông tin hàng' là ĐÚNG THIẾT KẾ và là TEXTBOX cho phép nhập ⇒ SC-ORD-011 assert cứng vị trí + nhập được. ⇒ App hiện theo PRD (nhãn 'Khối lượng' / dropdown) = DEFECT UI, không phải TC sai. CÒN LẠI (QA tự làm, không hỏi BA): vibe-check bấm thật nút 'Tiếp theo' (hiện cam dù chưa chọn gì — nghi giới hạn ảnh tĩnh), gộp với verify hành vi chặn ảnh bắt buộc của RISK-ORD-09. GHI NỢ: SC-ORD-008/009/010/011 là CARRIED (v1.0) nhưng nay assert mạnh hơn — xem ORD/CHANGELOG.md §3.
+[Ghi chú cũ] ⚠️ KHÔNG lẫn với C-ORD-02 (ngưỡng cấu hình + cảnh báo mua bảo hiểm của BR-ORD-03, vẫn Resolved out of scope): ở đây KHÔNG có ô nhập số tiền, KHÔNG có rule chặn theo ngưỡng — mốc tiền chỉ là NHÃN PHỤ định nghĩa 3 mức định tính. ✅ Ảnh đồng thời XÁC NHẬN khối "ẢNH HÀNG *" đã có dấu * + bộ đếm "0/5" + helper "Bắt buộc ít nhất 1 ảnh · tối đa 5 ảnh" ⇒ BR01-01/BR18-02 đã build ở tầng UI, thu hẹp RISK-ORD-09. ⚠️ Nút "Tiếp theo" trên ảnh vẫn màu cam khi chưa chọn gì và chưa có ảnh — ngược KB-VIBE-03 + BR01-01; nghi là giới hạn ảnh tĩnh/demo ⇒ QA vibe-check bấm thật trước khi kết luận, KHÔNG log bug theo mỗi ảnh. Canonical: v1.1/ORD-dang-tin/risk_assessment.md mục "C-ORD-18".</t>
         </is>
       </c>
     </row>
@@ -2299,6 +2519,9 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" display="1. môi trường stag&#10;2. stag_anhdc4@fpt.com được, đã nghĩ việc điền đại thông ví dụ đi, khi vibe test t sẽ cung cấp dữ liệu đúng &#10;3.  @fpt.vn, @gmail.com&#10;4. không tìm thấy thôi, không báo gì &#10;5. đúng nhé  " r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2311,219 +2534,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>ACT-hoat-dong — Hoạt động (Đơn của tôi)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-ACT-02</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Nhãn 2 tab + tên màn: PRD gọi "Đang chạy"/"Hoàn tất" + màn "Đơn của tôi"; app STG hiển thị "Đang diễn ra"/"Đã hoàn thành" + bottom nav "Hoạt động". PRD nhất quán ở 3 chỗ độc lập nên không phải lỗi đánh máy.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.17.1 EMP-05/EMP-06 · §6.2 AC-09.1.01 (tr.19,51) vs app STG (KP-01 §3 KB-ORD-07, 2026-07-27)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Nhãn nào là chuẩn để assert — theo PRD hay theo app?
 (b) Nếu PRD chuẩn: đây là defect UI cần dev sửa, hay PRD viết theo bản thiết kế cũ (app không cần đổi)?
 (c) Tên màn trên bottom nav ("Hoạt động") có đổi theo tên PRD ("Đơn của tôi") không?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-ACT-001 đang tạm hạ phần nhãn xuống ghi nhận (không assert cứng); nhãn tab còn xuất hiện trong Steps của rất nhiều TC ở ACT và các module khác — chốt muộn phải sửa rải rác</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>a. Đơn của tôi. Tab Đang diễn ra|Đã hoàn thành 
 b. PRD Ba chưa cập nhật nhé, 
 c. Vẫn là Hoạt động</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Theo APP: tiêu đề màn 'Đơn của tôi' · tab 'Đang diễn ra' / 'Đã hoàn thành' · bottom nav 'Hoạt động'. PRD chưa cập nhật (không phải defect). SC-ACT-001 assert cứng.
 — Ghi chú cũ: Nên gộp 1 lượt hỏi BA cùng C-ORD-09 (nhãn "Loại hàng") vì cùng bản chất doc ⟷ app</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="90" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-ACT-01</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Tap vào card đơn ở màn Hoạt động mở màn "Chi tiết tin" (public, module FEED) hay "Theo dõi đơn" (role-aware, module DLV)? Hai màn khác bản chất, không chỉ khác tên gọi.</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-06 KP-01 §3 KB-ORD-07 dòng 5 vs DOC-v1.0-02 §3.7 đoạn 2</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Tap card ở màn Hoạt động dẫn tới đích nào — "Chi tiết tin" hay "Theo dõi đơn"? PRD v1.1 không nêu đích điều hướng.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-ACT-011 vẫn ở dạng [GAP] (chỉ ghi nhận đúng đơn, không assert theo tên màn). Nếu đích thật là "Chi tiết tin", cần kiểm tra lại có lặp bug C-ASN-02 không (chủ tin thấy nút "Tôi mang giúp được" trên đơn của mình)</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Đọc lại ver cũ xem có hong , chỗ này không đổi nhé ,(đang diễn ra thì ra màn hình theo dõi đơn, hoàn thành chưa tặng quà thì ra màn hình tặng qùa </t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Đang diễn ra → 'Theo dõi đơn'; Đã hoàn thành chưa tặng quà → màn 'Tặng quà'. Lưu ý: KP-01 v1.0 KB-ORD-07 dòng 5 ghi 'Chi tiết tin' — hết hiệu lực. Các ô còn thiếu → C-ACT-03.
 — Ghi chú cũ: Open từ 2026-09-07, PRD v1.1 không làm rõ thêm</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-ACT-03</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>BA mới trả lời 2 ô (Đang diễn ra; Hoàn thành chưa tặng quà). Ma trận thật là trạng thái × vai × đã/chưa tặng quà.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-ACT-01 · DOC-v1.1-01 §8.12.3 (tr.46) · KP-01 KB-ORD-07 dòng 6</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Tap card mở màn nào khi:
 (a) Đã hoàn thành + ĐÃ tặng quà (vai Người gửi)?
@@ -2532,67 +2755,133 @@
 (d) Đơn 'Có sự cố' / 'Hẹn giao lại' / 'Đang hoàn hàng' → Theo dõi đơn?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-ACT-009/010/011 chỉ assert được 2 ô đã chốt</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — trước generate-tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a, ra màn hình theo dõi đơn
+b. theo dõi đơn
+c. Theo dỡi đơn
+d. theo dõi đơn
+=&gt; hoàn thành nhưng chưa tặng quà thì người gởi sẽ ra màn hình tặng quà, còn lại ra màn theo dõi đơn , tin hết hạn thì sẽ không cho tương tác
+</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (a) Hoàn thành ĐÃ tặng quà (Sender) → 'Theo dõi đơn'. (b) vai Carrier/Receiver ở tab Đã hoàn thành → 'Theo dõi đơn'. (c) đơn RETURNED/EXPIRED → 'Theo dõi đơn' (riêng tin đã Hết hạn thì KHÔNG cho tương tác — đối chiếu C-ORD-17). (d) đơn INCIDENT/RESCHEDULED/RETURNING → 'Theo dõi đơn'. Tóm gọn: CHỈ 'Hoàn thành + CHƯA tặng quà' (Sender) → màn 'Tặng quà'; MỌI trường hợp còn lại → 'Theo dõi đơn' (trừ tin Hết hạn không tương tác được). CL-ACT-03 ĐÓNG HẲN. (Đã đồng bộ vào ACT-hoat-dong/risk_assessment.md cùng ngày.)
+— Ghi chú trước đó: 🔴 Cao — trước generate-tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-ACT-04</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>PRD v1.1 có 12 trạng thái (v1.0: 5) nhưng không nói trạng thái nào ở tab nào. Rule v1.0 (BA-chat 07/2026) 'đơn Đã huỷ ẩn khỏi cả 2 tab' ngược PRD §8.12.3 cho mọi vai 'Xem lý do' đơn đã huỷ. Tin OFFER 'xem lại được ở Đơn của tôi' nhưng không nói ở đâu.</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 (demo không hỗ trợ câu c) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.12.2/§8.12.3 (tr.45-46) · AC-19.1.01 (tr.23) · KP-01 KB-ORD-07 dòng 7</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>(a) Hẹn giao lại / Đang hoàn hàng / Có sự cố → tab Đang diễn ra? Đã trả người gửi / Hết hạn → tab Đã hoàn thành?
 (b) Đơn 'Đã huỷ' vẫn ẩn khỏi cả 2 tab (rule v1.0) hay nay hiện ở tab Đã hoàn thành kèm lý do?
 (c) Tin OFFER (tuyến đường) hiện ở tab nào, card trông thế nào, nhãn trạng thái gì, tap mở màn nào?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SC-ACT-004/005/007/015 (đối chứng Đã huỷ ⟷ Đã trả người gửi) phụ thuộc trực tiếp</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — trước generate-tc</t>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. hoàn thành nhé 
+b. ẩn nhé 
+c. Tab đang diễn ra, card thế nào thì vào link demo xem, nhãn thì vào link demo xem nhé , tab mở màn theo dõi đơn </t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): (a) 'Hẹn giao lại/Đang hoàn hàng/Có sự cố' → tab 'Đang diễn ra' — ĐÃ CHỐT theo BA. (b) đơn 'Đã huỷ' vẫn ẨN khỏi cả 2 tab — ĐÃ CHỐT theo BA. (c) đã thử đăng tin OFFER trên demo để soi card/nhãn ở tab 'Đang diễn ra', nhưng gặp ĐÚNG giới hạn demo đã ghi ở C-ORD-16 (vòng 2) / C-ASN-03: demo không tạo tin OFFER độc lập (ghi đè lên đơn NEED đang có, không sinh thêm card nào ở 'Đơn của tôi') ⇒ KHÔNG quan sát được hình dạng card/nhãn trạng thái cho tuyến OFFER. Cần BA gửi ảnh chụp màn hình thật (STG hoặc Figma) thay vì yêu cầu tự thao tác qua bản demo này.
+— Ghi chú trước đó: 🔴 Cao — trước generate-tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="109.5" customHeight="1" s="15">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>C-ACT-04 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Câu (c) duy nhất còn lại: hình dạng/nhãn card của tin OFFER ở tab "Đang diễn ra" — demo không dựng được (cùng giới hạn với C-ORD-16).</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved — QA tự verify qua demo 2026-09-17, không cần BA trả lời</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 §8.12.2 (tr.45) · ảnh 00_input/v1.1/design/ORD_08_dangtin_offer_ghide_len_don_dang_co.png (bằng chứng giới hạn demo)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Tin OFFER hiện ở tab "Đang diễn ra" của "Đơn của tôi" với card trông như thế nào (thông tin gì hiện trên card) và nhãn trạng thái ghi gì? (Đích tap card đã chốt = "Theo dõi đơn", không cần hỏi lại.) Xin gửi ảnh chụp màn hình thật vì demo không dựng được tin OFFER độc lập.</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>SC-ACT-004/005/015 (card + nhãn tin OFFER) chưa assert được</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>BA/PM</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>ngoài màn hình trạng chủ - &gt;Click vào  Hoạt động se  xem được mà sao lại giới hạn ??→ kiểm tra lại qua mcp nhé</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Duy nhất 1 câu còn lại của C-ACT-04 — (a)(b)(d) đã Resolved 2026-09-17.
+⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2): ACT-hoat-dong/risk_assessment.md · C-ACT-04 ĐÓNG HẲN 2026-09-17 — đã tự verify qua demo theo đúng chỉ dẫn BA (vào tab Hoạt động → Đang diễn ra): card OFFER title 'Nhận giao hàng &lt;tuyến&gt;', badge 'Chờ ghép', CTA 'Chạm để xem tuyến đường của bạn'. Không cần trả lời thêm.</t>
         </is>
       </c>
     </row>
@@ -2613,138 +2902,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col hidden="1" width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col hidden="1" width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col hidden="1" width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col hidden="1" width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>USR-tai-khoan — Tài khoản &amp; Hồ sơ</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-18 — MỞ LẠI C-USR-07 sau vibe-test VR-003 (trước đó: 2026-09-16, hết điểm hỏi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-USR-05</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>3 trường trong BRD cũ (avatar, khu vực/văn phòng, kênh liên hệ) không xuất hiện ở bất kỳ đâu trong đặc tả FR15 ("Cập nhật thông tin") của PRD v1.1. Vibe-check demo 2026-09-16 đã thu hẹp câu hỏi: avatar chỉ là icon/chữ viết tắt tĩnh, không có control đổi ảnh ở cả trang Cá nhân lẫn màn "Cập nhật thông tin"; "khu vực/văn phòng" và "kênh liên hệ" không xuất hiện dưới bất kỳ tên gọi nào trên demo.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved (qua vòng 2)</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §A6 USR-02 L100 vs DOC-v1.1-01 §8.15.1 BR15-01 · §8.15.2 (tr.48-49); vibe-check demo 2026-09-16</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Avatar — demo cho thấy không có control đổi ảnh; xác nhận với BA/PM đây có đúng là thiết kế chính thức (chỉ đọc, lấy từ SSO) hay demo chưa cài đặt tính năng này?
 (b) "Khu vực/văn phòng" — có phải chính là "Địa chỉ mặc định" đổi tên, hay là trường riêng biệt đã bị bỏ?
 (c) "Kênh liên hệ" (USR-07, đã chốt out-of-scope ở v1.0) — v1.1 có mở lại không, hay bỏ hẳn?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-USR-002 (trang Cá nhân) đã hết gap về danh sách trường (C-USR-04 Resolved 2026-09-16); phần còn treo chỉ là 3 câu hỏi (a)(b)(c) ở trên, không chặn generate-tc</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>a. load từ hiris và không cho phép chỉnh sửa ??
 b. Khu vực/văn phòng sẽ load giá trị tại Địa chỉ mặc định, các trường địa chỉ lấy hàng/giao hàng, điểm xuất phát → sẽ load theo địa chỉ mặc định của account ?
 b. Bỏ hẳn nhé</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>CẬP NHẬT 2026-09-16: đóng hẳn qua dòng vòng 2 (BA trả lời (a)(b)).
 — KẾT LUẬN (theo BA) 2026-09-16: (c) 'Kênh liên hệ' BỎ HẲN (BA ghi nhãn 'b' lần 2 — hiểu là câu c) → SC-USR-010 assert không tồn tại. (a)(b) BA để dấu '?' và (b) sinh rule prefill địa chỉ mới ngoài PRD → dòng vòng 2.
@@ -2752,28 +3041,28 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-USR-05 (vòng 2)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>(a) BA: 'load từ hiris và không cho phép chỉnh sửa ??' · (b) BA: 'Khu vực/văn phòng load giá trị tại Địa chỉ mặc định, các trường địa chỉ lấy hàng/giao hàng, điểm xuất phát → load theo địa chỉ mặc định của account ?'. PRD hiện: địa chỉ lấy hàng = địa chỉ mặc định; địa chỉ GIAO = tự điền từ danh bạ người nhận (AC-04.1.01); điểm xuất phát OFFER = 'vị trí làm việc' (§8.2.2).</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.1.4 (tr.35) · AC-04.1.01 (tr.17) · §8.2.2 (tr.36) · §8.15.2 (tr.49)</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(1) Xác nhận (a) và (b) — bỏ dấu '?'. Nếu HRIS có ảnh thì app hiện ảnh hay chữ viết tắt?
 (2) Địa chỉ GIAO HÀNG load theo địa chỉ mặc định của NGƯỜI GỬI (trùng địa chỉ lấy hàng — vi phạm 'phải khác địa chỉ lấy') hay của NGƯỜI NHẬN tra theo email?
@@ -2782,17 +3071,17 @@
 (5) Dòng thứ 3 BA đánh 'b' — đúng là trả lời câu (c)?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-USR-002 (avatar), SC-ORD-025/058 (prefill địa chỉ), SC-ORD-039..040 (OFFER) chưa assert được</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>(BA trả lời 2026-09-16, 5 lượt)
 (1a) Avatar: hiển thị CHỮ VIẾT TẮT không dấu, viết hoa, lấy chữ cái đầu của 2 từ cuối trong tên (Trần Văn A → VA; Trần A → TA; Đặng Ánh → DA). Avatar trang Cá nhân và màn Cập nhật thông tin là MỘT. Không cho sửa. Tên luôn ≥ 2 từ.
@@ -2803,76 +3092,76 @@
 (4) Chưa trả lời — chuyển sang C-HOME-04.</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: C-USR-05 RESOLVED. Đã áp vào analyze USR (SC-USR-002/016/020..024) + TC fragment TC-USR-v1.1.md. Câu (4) theo dõi ở C-HOME-04. ⚠️ Prefill giao hàng/điểm xuất phát có home ở ORD (SC-ORD-025/058) + ASN — chưa cập nhật SC 2 module đó. ⚠️ Rule ô địa chỉ chọn từ danh sách + điểm xuất phát KHÁC PRD (§8.15.2 "Văn bản ≤200", §8.2.2 "vị trí làm việc") ⇒ nhờ BA cập nhật PRD.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-USR-06</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Trang Cá nhân (demo + v1.0) hiện badge 'Hạng Đồng hành'; SC-USR-007 (v1.0) assert badge TỒN TẠI. PRD v1.1 cấm mọi hình thức tier/xếp hạng vĩnh viễn (BR14-03, AC-26.1.01, §4 Out of Scope) — cùng lý do ★★★★★ đã thành defect.</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR14-03 (tr.48) · AC-26.1.01 (tr.27) · §4 Out of Scope (tr.9) · ảnh USR_01</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Badge 'Hạng Đồng hành' là (a) defect cần gỡ theo BR14-03, hay (b) nhãn trang trí cố định (không phải hạng) được giữ — nếu (b) thì PRD cần ghi ngoại lệ?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-USR-007 ⟷ SC-USR-006/SC-GIFT-011 cho kết luận ngược nhau; tạm không assert badge</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>Hạng đồng hành ko hiện nhé (BA 2026-09-16)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Badge "Hạng Đồng hành" KHÔNG hiển thị (khớp BR14-03). SC-USR-007 lật chiều (assert KHÔNG có badge), SC-USR-011 cập nhật cấu trúc header — cả hai MODIFIED. Demo còn badge ⇒ STG còn hiện là defect.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="7" ht="150" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>— (đề nghị BA cập nhật PRD)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Các rule BA đã trả lời cho màn "Cập nhật thông tin" nhưng PRD v1.1 chưa ghi hoặc ghi khác — cần BA cập nhật PRD để dev làm đúng.</t>
         </is>
@@ -2882,12 +3171,12 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.15 · §8.15.1 BR15-01/02 · §8.15.2 (tr.48-49) · §8.2.2 (tr.36) · AC-30.2.01 (tr.28)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>(1) Icon cạnh Email công ty là KHIÊN (PRD ghi "icon khoá").
 (2) Số điện thoại mặc định load từ HRIS; bắt đầu bằng 0, đúng 10 ký tự, tất cả là số (khoảng trắng, +84, chữ đều không hợp lệ).
@@ -2898,40 +3187,40 @@
 BA cập nhật PRD theo các rule trên (đã trả lời 2026-09-16)?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>Không chặn generate-tc (TC đã viết theo câu trả lời BA). Nếu dev làm theo PRD cũ ⇒ TC-USR-002/008/012/021/025..037 FAIL hàng loạt dù dev cho là đúng.</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">PRD cập nhật sau nhé </t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: BA nhận cập nhật PRD sau (chưa có hạn). TC giữ theo câu trả lời BA; theo dõi ở USR-tai-khoan/CHANGELOG.md §3 Nợ #4 — khi có PRD bản sửa ⇒ /analyze --update đối chiếu lại.
 — Ghi chú cũ: 🟡 Trung bình — gửi BA cùng lượt vòng 2</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="8" ht="90" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>— (chuỗi thông báo lỗi SĐT)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>PRD không có nội dung thông báo lỗi khi số điện thoại mặc định để trống / sai định dạng. TC đang dùng TẠM chuỗi của demo.</t>
         </is>
@@ -2941,12 +3230,12 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR15-02 · AC-30.1.02 (tr.28, 48) · demo DOC-v1.1-02</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Chuỗi thông báo chính thức là gì?
 (a) Để trống — demo: "Vui lòng nhập số điện thoại"
@@ -2954,30 +3243,81 @@
 Giữ như demo hay chuỗi khác?</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>TC-USR-016/017/019/020/036 đang assert chuỗi demo — chuỗi thật khác thì sửa 5 TC.</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">lấy theo demo đúng r nhé </t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: Chuỗi demo là CHÍNH THỨC — trống: 'Vui lòng nhập số điện thoại' · sai định dạng: 'Số điện thoại không hợp lệ (10 số, bắt đầu bằng 0)'. Đã bỏ chữ 'tạm' ở TC-USR-016/017/019/020/036 + test_data_catalog.
 — Ghi chú cũ: 🟢 Thấp — không chặn, chỉ ảnh hưởng Expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>C-USR-07</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Địa chỉ mặc định để RỖNG có hợp lệ không, và có đường nào để XOÁ địa chỉ đã lưu? — Đây chính là câu (v) của C-USR-05 ("còn cho bỏ trống không, PRD ghi Không bắt buộc?"); BA CHƯA BAO GIỜ trả lời thẳng câu này nhưng C-USR-05 vẫn bị đóng Resolved ở lượt 5 (2026-09-16) =&gt; câu hỏi rơi mất, nay vibe-test làm nổi lại.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Open — mở lại 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 §8.15.2 (địa chỉ mặc định ghi "Không bắt buộc") · BR15-05 · AC-30.1.01</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>(a) Địa chỉ mặc định RỖNG có phải trạng thái hợp lệ của hồ sơ không? Nếu có, các màn tiêu thụ nó (ORD địa chỉ lấy hàng, ASN điểm xuất phát) xử lý ra sao khi rỗng?
+(b) Người dùng có đường nào để XOÁ địa chỉ đã lưu về rỗng không? (ô chỉ nhận giá trị chọn từ danh sách gợi ý — C-USR-05 đã chốt KHÔNG nhận text tự do)
+(c) Nếu KHÔNG cho rỗng thì app phải chặn ở đâu — disable nút Lưu, hay báo lỗi dưới field như BR15-02 làm với SĐT?</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>TC-USR-029 (đang FAIL kép, 1 vế đã hết hiệu lực sau khi bug B1 bị rút lại) · TC-USR-030 cùng dải · SC-USR-019, SC-USR-020</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>BA/PM</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>(chưa trả lời)</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>DỮ KIỆN THỰC NGHIỆM từ vibe-test VR-003 (2026-09-18, tài khoản MNV 00002352): đã bấm "Lưu thay đổi" 2 LẦN LIÊN TIẾP với ô "Địa chỉ mặc định" để TRỐNG HOÀN TOÀN — app LƯU THÀNH CÔNG cả 2 lần, không chặn, không báo lỗi dưới field, điều hướng về màn "Cá nhân" y như khi dữ liệu đầy đủ; mở lại màn thì SĐT persist đúng, địa chỉ vẫn rỗng.
+⚠️ ĐỪNG LẪN VỚI BUG-008: BUG-008 = app không NẠP dữ liệu HRIS vào form; C-USR-07 = có được phép LƯU rỗng hay không. Fix BUG-008 xong thì C-USR-07 VẪN CÒN cần BA trả lời.</t>
         </is>
       </c>
     </row>
@@ -2998,109 +3338,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>HOME-trang-chu — Trang chủ</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="120" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="120" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-HOME-04</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>'Khu vực của người dùng' là điều kiện lọc 'Tin mới' (AC-11.1.01/11.2.01, EMP-01) và Bảng tin ('cùng khu vực / thuận tuyến') nhưng PRD không định nghĩa. BA trả lời (C-USR-05, 2026-09-16): khu vực/văn phòng = địa chỉ mặc định, và địa chỉ mặc định CHỌN TỪ DANH SÁCH VĂN PHÒNG (file location_address_catalog.xlsx — có mã tỉnh province_code, area_code), không còn là văn bản tự do.</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>🟡 Partially Resolved — hỏi vòng 2</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 — → ĐÃ ĐÓNG ở vòng 3 (2026-09-17)</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-11.1.01/11.2.01 (tr.19-20) · §5.1 (tr.10) · EMP-01/04 (tr.51)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) 'Khu vực' = tỉnh/thành, văn phòng (HRIS), hay suy từ địa chỉ mặc định?
 (b) Tin cần gửi khớp khu vực theo điểm lấy, điểm giao hay cả hai?
@@ -3108,30 +3448,30 @@
 (d) Hồ sơ chưa có khu vực thì thấy tin toàn quốc?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-HOME-019/025 không dựng được Given '12 tin trong khu vực'</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a. suy tu mặc định nhé 
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>a. suy tu mặc định nhé 
 b. cả 2
 c. hiện tại lấy theo data từ file, thêm thì dev bổ sung trong db thôi
-d. ụa tin là load toàn quốc mà, đâu load theo khu vực? Tìa liệu có mô tả à </t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
+d. mỗi account login sẽ thấy tin đăng trên toàn quốc, không có theo khu vực (VD account có địa chỉ thuộc miên nam vẫn thấy được tin đăng ở miên bắc )</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: (a) khu vực suy từ địa chỉ mặc định · (b) khớp cả điểm lấy + giao · (c) danh mục văn phòng do dev thêm trong DB. NHƯNG (d) 'tin load toàn quốc, không theo khu vực' ⇒ mâu thuẫn (a)(b) và PRD AC-11.x/EMP-01/§5.1 ⇒ dòng vòng 2. Tạm viết Given toàn quốc cho SC-HOME-019/025, SC-FEED-001/013; chưa assert chữ 'trong khu vực'.
 — Ghi chú cũ: CẬP NHẬT 2026-09-16: địa chỉ mặc định nay là 1 văn phòng trong danh mục (có mã tỉnh/area) ⇒ câu (a) có thể chốt theo mã tỉnh hoặc văn phòng — vẫn cần BA trả lời.
@@ -3139,13 +3479,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-HOME-05</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>C-HOME-02 (chốt theo demo): section 'Đơn của tôi' ẨN khi không có đơn ⇒ SC-HOME-010. Nhưng PRD EMP-02: section hiện empty state 'Bạn chưa có đơn nào đang chạy' + CTA 'Tạo đơn gửi hàng' ⇒ SC-HOME-026. Hai SC không thể cùng PASS.</t>
         </is>
@@ -3155,122 +3495,122 @@
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 EMP-02 (tr.51) · ảnh HOME_03 · C-HOME-02</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Khi không có đơn đang chạy, Trang chủ ẨN section 'Đơn của tôi' hay HIỆN empty state EMP-02? Nếu tuỳ điều kiện (vd chưa từng có đơn ⟷ có đơn nhưng đã đóng hết) thì điều kiện là gì?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-HOME-010 ⟷ SC-HOME-026 mâu thuẫn — tạm hạ cả 2 xuống ghi nhận</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">hiện emp state chứ ko ẩn nhé </t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: Không có đơn đang chạy ⇒ HIỆN empty state EMP-02 ('Bạn chưa có đơn nào đang chạy' + CTA 'Tạo đơn gửi hàng'), KHÔNG ẩn. SC-HOME-026 assert cứng; SC-HOME-010 (ẩn section) DEPRECATED; vế 'ẩn' của C-HOME-02 hết hiệu lực. Demo HOME_03 đang ẩn ⇒ STG ẩn là defect.
 — Ghi chú cũ: 🔴 Cao — SC mâu thuẫn</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-HOME-06</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Hero 'N đơn đã giúp' và cụm cộng đồng 'N đơn · M người' không có công thức đếm (chỉ có ví dụ giá trị 0 ở AC-26.2.01).</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>🟡 Partially Resolved — hỏi vòng 2</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §7.1 (tr.30) · AC-26.2.01 (tr.27) · EMP-03 (tr.51) · BR14-04 (tr.48)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(a) Hero của Người gửi / Người nhận (không 'giúp' đơn nào) hiện gì — luôn 0?
 (b) 'N đơn · M người': N = đơn Hoàn thành toàn hệ thống hay trong khu vực? M = số người đã giúp (Carrier) hay mọi người tham gia? Có tính đơn Đã trả người gửi?
 (c) Số liệu cập nhật realtime hay theo chu kỳ?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-HOME-008/027 chỉ assert được giá trị 0</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>a. 0
-b. toàn hệ thống, người tham gia
+b. N là đơn toàn hệ thống, M là tổng số người tham gia app
 c. realtime</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-17: (a) tài khoản chưa từng giúp ⇒ hero = 0 (+SC-HOME-029) · (b) N = đơn toàn hệ thống, M = người tham gia · (c) realtime (+SC-HOME-030). SC-HOME-008 MODIFIED. Còn mơ hồ định nghĩa 'người tham gia' + đơn Đã trả người gửi ⇒ dòng vòng 2 (thấp); tạm không assert M.
 — Ghi chú cũ: 🟢 Thấp</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="200" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="7" ht="199.5" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-HOME-04 (vòng 2)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>BA trả lời (a) khu vực suy từ địa chỉ mặc định, (b) khớp cả điểm lấy và giao, (c) danh mục do dev thêm trong DB — nhưng (d) nói 'tin là load toàn quốc, đâu load theo khu vực? Tài liệu có mô tả à'. Hai vế ngược nhau. PRD CÓ mô tả lọc khu vực ở 4 chỗ: AC-11.1.01 'Trong khu vực của người dùng có 12 tin NEED' · AC-11.2.01/EMP-01 'Chưa có tin nào trong khu vực của bạn' · §5.1 'Hiển thị cho CBNV cùng khu vực / thuận tuyến' · EMP-04 'gợi ý mở rộng khu vực'.</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>🟡 Chờ BA — vòng 2</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 (chỉ còn câu 3, chuỗi empty state) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại) — → ĐÃ ĐÓNG ở vòng 3 (2026-09-17)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-11.1.01/AC-11.2.01 (tr.19) · §5.1 (tr.10) · EMP-01/EMP-04 (tr.51)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>(1) Xác nhận: 'Tin mới' ở Trang chủ và Bảng tin hiển thị tin NEED TOÀN QUỐC, KHÔNG lọc theo khu vực — đúng không? (PRD trang 19 + trang 10 đang ghi lọc theo khu vực.)
 (2) Nếu toàn quốc: câu (a)(b) 'khu vực suy từ địa chỉ mặc định, khớp cả 2 điểm' dùng cho việc gì — sắp xếp ưu tiên tin gần lên trước, hay chỉ dùng cho khớp tuyến/gợi ý (ASN)?
@@ -3278,74 +3618,138 @@
 (4) Thứ tự tin: mới nhất trước trên toàn quốc?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SC-HOME-019/025, SC-FEED-001/013 đang tạm viết Given toàn quốc, chữ empty state chưa assert. Nếu thực tế có lọc khu vực ⇒ sửa Given 4 SC + cần data ≥2 văn phòng khác khu vực. Empty state 'Tin mới' toàn quốc gần như không dựng được trên STG dùng chung.</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình — vòng 2 của câu BA tự mâu thuẫn</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>1. đúng
+2. Chỉ dùng cho khớp tuyến
+3. 
+4. mới nhất toàn quốc lên trước</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (1) đúng — 'Tin mới' ở Trang chủ/Bảng tin hiển thị tin NEED TOÀN QUỐC, KHÔNG lọc theo khu vực (xác nhận dứt điểm, thay thế mọi suy đoán trước đó). (2) khái niệm 'khu vực suy từ địa chỉ mặc định' CHỈ dùng để khớp tuyến (ASN), KHÔNG dùng để lọc Tin mới/Bảng tin. (4) thứ tự tin: MỚI NHẤT lên trước, trên phạm vi TOÀN QUỐC. CÒN TREO (3): BA để trống câu 'giữ chữ Chưa có tin nào trong khu vực của bạn (EMP-01) không? Gợi ý mở rộng khu vực (EMP-04) còn không, là nút hay chữ?' — vì đã xác định tin không lọc theo khu vực, 2 câu chữ EMP-01/EMP-04 gần như chắc chắn KHÔNG còn phù hợp (PRD viết theo giả định có lọc khu vực) nhưng cần BA xác nhận dứt điểm chuỗi empty state thay thế là gì trước khi viết TC cho SC-HOME-019/025 nhánh 0 tin.
+— Ghi chú trước đó: 🟡 Trung bình — vòng 2 của câu BA tự mâu thuẫn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="169.5" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-HOME-06 (vòng 2)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>BA chốt: hero tài khoản không giúp đơn nào = 0; cụm cộng đồng N = toàn hệ thống, M = 'người tham gia'; cập nhật realtime. Chưa rõ 'người tham gia' đếm ai và N có tính đơn Đã trả người gửi không.</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>🟡 Chờ BA — vòng 2</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved (Accepted — BA đề nghị bỏ qua, không có đặc tả)</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-HOME-06 · DOC-v1.1-01 AC-26.2.01 (tr.27) · BR14-04 (tr.48) · EMP-03 (tr.51)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>(1) M 'người tham gia' = số người KHÁC NHAU từng tham gia đơn Hoàn thành ở cả 3 vai (gửi / vận chuyển / nhận), chỉ Người vận chuyển, hay mọi CBNV đã dùng app?
 (2) N (đơn cộng đồng) có tính đơn 'Đã trả người gửi' không? (BR14-04 loại đơn này khỏi 'đơn đã giúp' cá nhân.)
 (3) Hero 'N đơn đã giúp' của 1 tài khoản = số đơn Hoàn thành mà tài khoản đó làm Người vận chuyển — đúng không?</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>SC-HOME-008/030 không assert được M; SC-HOME-029 (hero = 0) đang viết theo cách hiểu (3)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Thấp — không chặn</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1" s="12"/>
-    <row r="10" ht="120" customHeight="1" s="12"/>
-    <row r="11" ht="120" customHeight="1" s="12"/>
-    <row r="12" ht="120" customHeight="1" s="12"/>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cái này bỏ qua được không, chưa có đặc tả cụ thẻ ? Ver này đâu có update gì chỗ này </t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: BA đề nghị BỎ QUA câu này — 'chưa có đặc tả cụ thể, version này không cập nhật gì ở phần này'. CHẤP NHẬN theo đề nghị BA: giữ nguyên hiểu biết hiện tại (a) hero tài khoản chưa từng giúp = 0 (b) N = đơn toàn hệ thống, M = người tham gia (chưa định nghĩa chi tiết 'người tham gia' gồm ai, và N có tính đơn Đã trả người gửi không) (c) realtime. KHÔNG cần hỏi thêm BA — SC-HOME-008/030 giữ nguyên mức assert hiện có (không assert giá trị chính xác của M), ghi nhận là giới hạn đã biết, không phải gap chờ trả lời. CL-HOME-06 (vòng 2) ĐÓNG theo hướng Accepted/Deferred.
+— Ghi chú trước đó: 🟢 Thấp — không chặn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="109.5" customHeight="1" s="15">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>C-HOME-04 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Câu (3) duy nhất còn lại: chuỗi empty state của "Tin mới" khi 0 tin — vì đã xác nhận KHÔNG lọc theo khu vực (tin toàn quốc), 2 câu chữ EMP-01/EMP-04 trong PRD (viết theo giả định có lọc khu vực) gần như chắc chắn không còn đúng.</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved 2026-09-17 (vòng 3) — ĐÓNG HẲN</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 §8.17.1 EMP-01/EMP-04 (tr.51) · BA trả lời C-HOME-04 vòng 2 (2026-09-17): xác nhận tin load toàn quốc</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Vì Trang chủ/Bảng tin hiển thị tin NEED toàn quốc (không lọc khu vực) — khi không có tin NEED nào (0 tin), màn hiện chữ gì? Giữ nguyên "Chưa có tin nào trong khu vực của bạn" (EMP-01) hay đổi câu khác cho khớp việc không lọc khu vực? "Gợi ý mở rộng khu vực" (EMP-04) còn hiển thị không — nếu còn thì là nút bấm hay chỉ là chữ mô tả?</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>SC-HOME-019/025, SC-FEED-001/013 (nhánh 0 tin) chưa assert được chữ empty state</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>giữ nguyên nhé</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17 — C-HOME-04 ĐÓNG HẲN: GIỮ NGUYÊN chuỗi empty state đúng như PRD — EMP-01 "Chưa có tin nào trong khu vực của bạn" (Trang chủ · Tin mới) và EMP-04 "Chưa có tin nào" + gợi ý mở rộng khu vực hoặc đăng tin (Bảng tin), DÙ danh sách tin load toàn quốc (chốt ở vòng 2). ⇒ SC-HOME-025 + SC-FEED-013 (+ TC-FEED-013) bỏ rào "tạm ghi nhận chữ", assert CỨNG chuỗi PRD. ⚠️ Mâu thuẫn copy ⟷ logic là QUYẾT ĐỊNH THIẾT KẾ của BA, không phải defect — không mở lại CL, không tự sửa oracle; STG hiện chữ khác ⇒ FAIL (lệch tài liệu). ℹ️ PRD không nói "gợi ý mở rộng khu vực" là nút hay chữ ⇒ assert NỘI DUNG CHỮ, ghi nhận dạng hiển thị thực tế lúc chạy, không FAIL vì hình thức. Canonical: v1.1/HOME-trang-chu/risk_assessment.md mục "C-HOME-04 · ↳ BA trả lời vòng 3".</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1" s="15"/>
+    <row r="11" ht="120" customHeight="1" s="15"/>
+    <row r="12" ht="120" customHeight="1" s="15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -3366,212 +3770,212 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>ASN-ghep-noi — Ghép nối</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-ASN-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Wizard đăng tin không tạo listing độc lập trong Bảng tin — quan sát trên bản demo (prototype) chỉ có 1 đơn hàng duy nhất, đăng tin mới ghi đè đơn đang có thay vì tạo song song.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-06 KP-01 §4 KB-ASN-05 vs DOC-v1.0-02 §7 dòng 3</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Hiện tượng "đăng tin mới ghi đè đơn đang có, không tạo song song" là giới hạn kỹ thuật của bản demo, hay là hành vi thật cần fix trên app/backend?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>SC-ASN-018 ghi nhận với tiền đề 2 tin liên tiếp, chưa kết luận là bug. Nếu app STG cũng ghi đè đơn thì đây là vấn đề kiến trúc nghiêm trọng cần escalate ngay</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>Hiện tại không giói hạn đăng tin, đây là giới hạn bản demo</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Ghi đè đơn là giới hạn DEMO; app KHÔNG giới hạn số tin đăng ⇒ SC-ASN-018 hết GAP: đăng tin thứ 2 không được ghi đè tin thứ 1. Vẫn verify trên STG.
 — Ghi chú cũ: Cần xác nhận lại khi có backend thật (STG), không chỉ dựa vào demo</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="90" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-NTF-02</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Định nghĩa "khớp tuyến" cho auto-match: 2/3 tham số đã chốt qua PRD v1.1 (định nghĩa khớp điểm+ngày+buổi overlap, chu kỳ quét ≤60s). Còn thiếu "ngưỡng gộp thông báo" — không phải câu hỏi nghiệp vụ mà là giá trị cấu hình vận hành.</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D6/§D7 (BRD tự ghi "Nháp — chờ BA review") vs DOC-v1.1-01 §8.4 BR04-01/02/04</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Ngưỡng "trần thông báo khớp/ngày" (BR04-04) là bao nhiêu? PRD ghi "do admin cấu hình" nhưng không cho số cứng.</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-ASN-014 (RISK-ASN-08) không viết được TC boundary chính xác cho tới khi có giá trị thật; tạm thời viết TC dạng biến số, không hardcode</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>Admin vận hành</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không có ngường ngày, tài liệu bị dư → mỗi lần đăng Tôi nhận giao hàng thì bắn 5 thông báo/ 1 tin đăng, không có giới hạn ngày </t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: KHÔNG có trần thông báo theo ngày (BR04-04 dư, RISK-ASN-08 đóng). Thay bằng '5 thông báo / 1 tin đăng Tôi nhận giao hàng' — rule này chưa đủ định nghĩa → C-ASN-04. Lưu ý: đảo kết luận lần 2 (v1.0 theo tin OFFER → PRD theo ngày → nay theo tin đăng).
 — Ghi chú cũ: Home canonical của CL này ở module ASN; liên quan REQ-NTF-002 bên NTF</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-ASN-04</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Rule mới 'mỗi lần đăng Tôi nhận giao hàng bắn 5 thông báo / 1 tin đăng' — con số 5 trùng 'trần gợi ý 5 tin' của BR03-06 nhưng chưa rõ cùng 1 rule; PRD §8.4 còn trigger 'có tin NEED mới'.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>BA trả lời C-NTF-02 · DOC-v1.1-01 AC-21.1.01 (tr.24) · BR03-06 (tr.36) · §8.4 Trigger (tr.37) · NFR-04</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(a) Ai nhận 5 thông báo — người đăng tuyến (Carrier) được báo 5 tin cần gửi khớp?
 (b) Có &gt;5 tin khớp thì chọn 5 tin nào — theo ưu tiên BR03-06 (gần tuyến → thời gian đăng)? '5 thông báo' và 'trần gợi ý 5 tin' là CÙNG một rule?
@@ -3580,46 +3984,56 @@
 (e) Tuyến đã bắn đủ 5 rồi thì tin khớp đăng sau có còn được báo?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>SC-ASN-013/014 không viết được Then chính xác</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a, người đăng tín nhận
+b. ưu tiên thời gian đăng nhé (hiện tại phải tủng tuyến mới được ) → cùng 1 rule 
+c. đúng nhé 
+d. có gởi thêm nhé nếu chưa đủ 5 tin, nếu trước đó đã gởi 5 rồi thì không gởi thêm 
+e. chưa hiểu câu hỏi của m. đăng 1 tin tôi nhận giao hang nếu có &gt; 5 tin khớp tuyến thì bắn 5 tin thôi, bắn đủ 5 rồi ko bắn thêm, nếu đăng thêm 1 tin Tôi nhận giao hàng nữa thì bắn tiếp 5 tin (nếu đăng 2 tin Tôi nhân giao hàng thì tôi đa sẽ nhận được đén 10 thông báo)
+</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (a) người ĐĂNG TUYẾN (Carrier) là người nhận 5 thông báo. (b) chọn 5 tin theo ƯU TIÊN THỜI GIAN ĐĂNG (tin đăng trước ưu tiên trước) — ĐÂY LÀ CÙNG 1 RULE với 'trần gợi ý 5 tin' của BR03-06, không phải 2 rule khác nhau. (c) có &lt;5 tin khớp thì gửi đúng số đó; 0 tin thì không gửi. (d) tin cần gửi MỚI đăng sau khi tuyến đã đăng: NẾU tuyến CHƯA đủ 5 thông báo thì vẫn gửi thêm; NẾU tuyến đã bắn đủ 5 rồi thì KHÔNG gửi thêm cho tin mới đó. (e) mỗi tuyến (mỗi lần đăng 'Tôi nhận giao hàng') có trần ĐỘC LẬP 5 thông báo — đăng 2 tuyến thì tối đa nhận 10 thông báo (5+5), không cộng dồn chung 1 trần. CL-ASN-04 ĐÓNG HẲN — đủ định nghĩa để viết Then chính xác cho SC-ASN-013/014.
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-ASN-05</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Điều kiện khớp 'trùng điểm lấy và điểm giao' nhưng ô địa chỉ là văn bản tự do ≤200 ký tự (C-ORD-11). ⚠️ Cập nhật 2026-09-16: địa chỉ mặc định (prefill lấy hàng / giao hàng / điểm xuất phát) nay CHỌN TỪ DANH SÁCH VĂN PHÒNG (C-USR-05) — chưa rõ các ô địa chỉ trong wizard có cùng cơ chế không. PRD không định nghĩa phép so; cũng chưa định nghĩa phép so 'địa chỉ giao phải khác địa chỉ lấy' (RISK-ORD-12).</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR04-01 (tr.37) · §8.1.4 (tr.35) · §8.2.2 (tr.36) · §4 Out of Scope (tr.9)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>'Trùng' địa chỉ được so thế nào:
 (a) khớp chuỗi chính xác;
@@ -3628,67 +4042,79 @@
 Quy tắc này có dùng chung cho rule 'địa chỉ giao phải khác địa chỉ lấy' không?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>🔴 Không dựng được dữ liệu cho 4 nhánh SC-ASN-011; SC-ORD-063 không assert được</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>CẬP NHẬT 2026-09-16: nếu mọi ô địa chỉ đều chọn từ danh mục văn phòng thì "trùng điểm" có thể so theo mã văn phòng (id) ⇒ hỏi thêm BA điểm này.
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. chính xác + thời gian phù hợp 
+b. cái này chọn từ data load lên mà, đây phải nhập đâu, nên cần khớp data
+c. có </t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: (a) so khớp 'trùng điểm' = KHỚP CHÍNH XÁC (exact match) + điều kiện thời gian phù hợp (ngày/buổi overlap — cùng rule đã chốt ở BR04-01). (b) từ khi địa chỉ (lấy/giao/điểm xuất phát) đều CHỌN TỪ DANH MỤC VĂN PHÒNG (C-USR-05) thay vì gõ tự do, nên không cần thêm rule chuẩn hoá (bỏ khoảng trắng/dấu/hoa-thường) — 2 giá trị chọn từ cùng 1 danh mục thì khớp chuỗi chính xác là đủ, không có sai khác chính tả. (c) CÓ — cùng 1 phép so 'chính xác' áp dụng luôn cho rule 'địa chỉ giao phải khác địa chỉ lấy' (RISK-ORD-12). CL-ASN-05 ĐÓNG HẲN — SC-ASN-011 (4 nhánh) và SC-ORD-063 dựng được dữ liệu theo mã văn phòng (id).
+— Ghi chú trước đó: CẬP NHẬT 2026-09-16: nếu mọi ô địa chỉ đều chọn từ danh mục văn phòng thì "trùng điểm" có thể so theo mã văn phòng (id) ⇒ hỏi thêm BA điểm này.
 — 🔴 Cao — chặn generate-tc</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="120" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="8" ht="120" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-ASN-06</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Cùng tình huống 'tin đã có người nhận' nhưng 2 AC dùng 2 câu khác nhau theo 2 lối vào, và câu đó không nằm trong danh mục 15 thông báo.</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved (Accepted)</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-12.1.02 (tr.20) · AC-22.2.01 (tr.25)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>(a) Giữ 2 câu riêng ('Tin này đã có người nhận mang giúp' từ Bảng tin / 'Đơn này đã có người nhận mang giúp' từ thông báo khớp tuyến) hay thống nhất 1 câu?
 (b) Hiển thị dạng toast, popup hay push?</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Chỉ ảnh hưởng assert verbatim SC-ASN-006/010</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Thấp</t>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bỏ qua: lấy ừ 15 thông báo thôi nhé </t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-16: BA đề nghị BỎ QUA — chọn 1 câu bất kỳ trong danh mục 15 thông báo chính thức làm chuẩn, không cần định nghĩa câu riêng cho từng lối vào (Bảng tin / thông báo khớp tuyến). SC-ASN-006/010 assert theo câu đã có trong danh mục 15 thông báo (không tạo thêm biến thể câu chữ). CL-ASN-06 ĐÓNG theo hướng Accepted.
+— Ghi chú trước đó: 🟢 Thấp</t>
         </is>
       </c>
     </row>
@@ -3712,135 +4138,135 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>CNL-huy-don — Huỷ đơn / Huỷ nhận đơn</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-CNL-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>3 câu trong PRD cùng ám chỉ có 1 đường xử lý "huỷ không thường" do Admin vận hành thực hiện (từ IN_TRANSIT trở đi không còn huỷ thường; đơn INCIDENT phải qua admin hỗ trợ mới về COMPLETED) — nhưng PRD KHÔNG đặc tả bề mặt: không màn, không field, không ma trận quyền, không SLA.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 §8.11.1 BR11-04 (tr.44) · §8.11 dòng Actor (tr.44) · §6.2 AC-25.2.01 (tr.26)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Admin vận hành thao tác "huỷ không thường"/đóng đơn INCIDENT qua bề mặt nào — back-office riêng hay qua Google Form của FR16 (Báo sự cố)?
 (b) Đơn ở trạng thái INCIDENT kết thúc ở trạng thái nào, và ai là người chuyển trạng thái đó?
 (c) Trong lúc chờ xử lý, người dùng cuối (Sender/Carrier/Receiver) có thấy thông tin/thông báo gì không?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Non-blocking cho generate-tc (2 SC liên quan đều dạng ghi nhận/GAP) nhưng BLOCKING cho việc kết luận đơn có bị treo vĩnh viễn hay không (RISK-CNL-07) — nên nêu với PM trước khi execute</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">a. hiên tại chỉ  nhận báo cáo quá gg form, dev hỗ trợ tay, không có màn hình hay tool
 b. dev hỗ trợ đến trạng tùy ý (phụ thuộc dev)
 c. Không </t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Không có màn/tool admin; dev hỗ trợ tay qua báo cáo Google Form; trạng thái đích tuỳ dev; người dùng không thấy gì khi chờ. RISK-CNL-07 → Accepted (rủi ro vận hành: đơn Có sự cố có thể treo nếu dev không xử lý). SC-CNL-017 assert KHÔNG có bề mặt admin. Câu 'đơn VÀO trạng thái Có sự cố bằng cách nào' → C-TS-02.
 — Ghi chú cũ: Nếu app build đúng AC-25.2.01 mà không có đường tới admin thì đơn INCIDENT có thể treo vĩnh viễn — phát hiện ở khâu phân tích rẻ hơn nhiều so với phát hiện ở UAT</t>
@@ -3864,162 +4290,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>DLV-giao-nhan — Giao nhận &amp; Theo dõi đơn</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-DLV-02</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Chia sẻ vị trí (GPS-01) khi đang giao — mặc định bật hay tắt? Chính BRD tự đặt câu hỏi mở này, BA/PO từng trả lời "phase sau" nhưng chưa cho giá trị cụ thể.</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>✅ Resolved</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3 GPS-01 L251 · §D5 L311 vs DOC-v1.0-06 KP-01 §5 KB-DLV-04</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>GPS-01 (chia sẻ vị trí khi đang giao) có vào scope v1.1 không? Nếu có, giá trị mặc định là bật hay tắt?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>REQ-DLV-013 hiện là gap SC có chủ đích, không viết SC khẳng định. Ma trận trạng thái "Đang giao" không có control này ở bất kỳ vai nào — khả năng cao bề mặt chưa tồn tại</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/PM</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không có chức năng này </t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>KẾT LUẬN (theo BA) 2026-09-16: Không có chức năng chia sẻ vị trí ⇒ GPS-01 out of scope, không viết SC. (Đính chính kèm: COST-01 cũng out of scope theo §4 PRD 'ghi nhận chi phí vận chuyển'.)
 — Ghi chú cũ: Nếu PM chốt vào scope thì cần chạy lại /analyze --update để bổ sung SC mới</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-DLV-05</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>AC-18.1.01: 'Theo lịch hẹn, đơn quay lại Đang giao' — không rõ tự động hay Carrier bấm. Từ điển cho RESCHEDULED → RETURNING nhưng không AC nào mô tả. Timeline chỉ 5 mốc trong khi có thêm Hẹn giao lại / Đang hoàn hàng / Đã trả / Có sự cố.</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 (đã vibe-check demo) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-18.1.01 (tr.23) · BR09-05 (tr.42) · §8.12.2/§8.12.3 (tr.45-46) · §5.1 Timeline (tr.10)</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) Đến giờ hẹn, đơn TỰ chuyển về 'Đang giao' hay Carrier bấm 'Giao lại'? Giao sớm hơn lịch hẹn được không?
 (b) 'Hẹn giao lại' → 'Đang hoàn hàng': ai bấm, ở màn nào, có nhập lịch hẹn mới?
@@ -4027,92 +4453,107 @@
 (d) Thanh tiến trình 5 mốc hiển thị các trạng thái mới ở mốc nào / nhãn gì?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-DLV-016, SC-DLV-031, SC-DLV-050 chưa assert được</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1" s="12">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có click Không thể liên lạc cho người nhận? Để chup ui hay thao tác thử chưa ? Chưa thì làm giúp t liền → chỗ này cần thao tác nhiều trên link demo để lấy thêm ui nhé 
+a. đúng 
+b. người vẫn chuyển chọn Càm hàng về 
+c. không giới hạn
+d. đang giao </t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2, role Người vận chuyển): đã thao tác thật trên https://giangdc.github.io/foxeco_demo/FoxEcoQC — Đang giao → 'Đã đến địa điểm giao hàng' → 'Không thể liên lạc cho người nhận?' → 'Không thể liên lạc với người gửi và người nhận?' → modal 'Chưa liên lạc được?' → 'Xử lý đơn hàng' → chọn 'Cầm hàng về'. Quan sát: (b) chọn 'Cầm hàng về' hiện thêm mục 'Sau đó bạn sẽ *' với 2 lựa chọn — 'Tôi sẽ giao lại sau' (hẹn thời gian quay lại giao) / 'Tôi sẽ trả về cho người gửi' — và một khối 'Hẹn trả hàng *' (Ngày hẹn, Từ/Đến giờ, Nơi nhận lại hàng) do CHÍNH Carrier tự nhập ngay tại màn 'Xử lý đơn hàng' (không phải màn riêng, không phải hệ thống tự sinh giờ hẹn). (c) Không thấy bộ đếm/giới hạn số lần hẹn giao lại trên UI. (d) Thanh tiến trình vẫn giữ nguyên 5 mốc cũ (Chờ ghép/Lấy hàng/Đang giao/Đã giao/Hoàn thành) — không có mốc phụ cho 'Hẹn giao lại'/'Đang hoàn hàng', trạng thái đơn vẫn hiển thị 'Đang giao'. CÒN THIẾU (không thấy qua demo tĩnh — cần hỏi lại BA/Dev): đến đúng giờ hẹn, đơn có TỰ động chuyển về 'Đang giao' hay Carrier phải tự bấm? Thanh 5 mốc có được bổ sung nhãn phụ ở bản thật không, hay giữ nguyên 'Đang giao' xuyên suốt như demo?
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1" s="15">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-DLV-06</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>3 chỗ PRD mô tả 3 cấu trúc khác nhau cho luồng 'Không liên lạc được người nhận': BR08-02 danh sách 4 bước (quầy lễ tân trước bảo vệ, bước 1 'giao cho người uỷ quyền đã khai sẵn'); AC-16.1.01 modal 2 hướng; AC-17.1.01 + §8.8.2 chốt bảo vệ trước quầy lễ tân. Demo: modal 2 hướng.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Chờ BA — vòng 2 (đã đối chiếu ảnh DLV_04/05, cần xác nhận + câu d mới) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR08-02 (tr.41) · AC-16.1.01/17.1.01 (tr.22) · §8.8.2 (tr.42) · ảnh DLV_04/05</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>(a) Cấu trúc chuẩn: modal 2 hướng (Liên hệ người gửi / Xử lý đơn hàng) + màn 3 lựa chọn?
 (b) Thứ tự đúng: chốt bảo vệ → quầy lễ tân, hay quầy lễ tân → chốt bảo vệ?
 (c) Bước 'giao cho người uỷ quyền đã khai sẵn' chọn ở đâu — chính là lựa chọn 'Người được uỷ quyền' (có prefill) ở màn Xác nhận giao hàng?</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-DLV-043 đang assert theo BR08-02 — nhiều khả năng FAIL oan</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — trước generate-tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1" s="12">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vào link demo, thao tác vào các btn, link  kiểm tra lại các ui còn thiến và đặt lại câu hỏi sau nhé </t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>SỬA LẠI 2026-09-17 (sau khi rà lại 00_input/v1.1/design/ — QA GiangDC2 xin lỗi vì lượt vibe-check ban đầu hôm nay bỏ sót ảnh có sẵn): việc verify hôm nay LẶP LẠI phần lớn vibe-check đã làm 2026-09-15 (ảnh DLV_04/DLV_05, đã ghi trong risk_assessment.md + CHANGELOG §1 dòng 2026-09-15) — không phải phát hiện mới. Bổ sung 1 chi tiết bị bỏ sót ở lượt hôm nay: tại tầng (2) 'Liên hệ người gửi', khi chọn 'Quầy lễ tân' hoặc 'Quầy bảo vệ' ở field 'Giao cho', UI hiện thêm khối 'NGƯỜI NHẬN TẠI QUẦY' với 2 ô 'Họ tên người trực quầy' + 'Số điện thoại' (xem ảnh DLV_04) — chưa rõ 2 ô này bắt buộc hay tuỳ chọn, PRD không nhắc tới. Câu hỏi bổ sung cho BA: (d) 2 ô 'Họ tên người trực quầy'/'SĐT' có bắt buộc không? Có dùng để gọi xác nhận lại không, hay chỉ lưu ghi chú?
+— Ghi chú trước đó: CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): đã thao tác đủ 4 tầng màn hình trên demo. Cấu trúc CHUẨN quan sát được: (1) màn 'Xác nhận đã giao' → nút 'Không thể liên lạc cho người nhận?' → (2) MÀN (không phải modal) 'Liên hệ người gửi' — hiện SĐT người gửi + nút Gọi + đã có sẵn field 'Giao cho *: Người được uỷ quyền / Quầy lễ tân / Quầy bảo vệ' NGAY TẠI ĐÂY (không tách riêng bước) + nút 'Không thể liên lạc với người gửi và người nhận?' → (3) MODAL 2 hướng 'Chưa liên lạc được?' ('Tôi sẽ chờ &amp; gọi lại' / 'Xử lý đơn hàng') → (4) màn 'Xử lý đơn hàng' với 3 phương án theo đúng THỨ TỰ: 'Gửi tại chốt bảo vệ' (liệt kê TRƯỚC) → 'Gửi tại quầy lễ tân' (SAU) → 'Cầm hàng về'. (b) Thứ tự bảo vệ-trước-lễ-tân KHỚP AC-17.1.01/§8.8.2, NGƯỢC BR08-02 (BR08-02 lỗi thời/dư, đề nghị BA xác nhận bỏ). (c) Bước 'giao cho người uỷ quyền đã khai sẵn' của BR08-02 = đúng field 'Giao cho' ở tầng (2), nhưng gộp chung với 2 lựa chọn quầy, không phải bước tách riêng như BR08-02 mô tả. (a) Cấu trúc thật là chuỗi 4 tầng (màn → màn → modal → màn), KHÔNG phải chỉ 'modal 2 hướng' đơn thuần như AC-16.1.01 gợi ý. Đề nghị BA XÁC NHẬN cấu trúc 4 tầng trên là chuẩn (không phải giới hạn riêng của bản demo) để dùng làm oracle chính thức cho SC-DLV-043, thay thế BR08-02/AC-16.1.01.
+— Ghi chú trước đó: 🔴 Cao — trước generate-tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" s="15">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>C-DLV-07</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>PRD có 3 bộ mốc 'nhắc' + 'chuyển admin hỗ trợ' (2h/4h khi chờ xác nhận nhận hàng; 4h/cuối ngày/24h khi giữ tại quầy; 24h quá lịch hẹn) nhưng danh mục 15 thông báo KHÔNG có loại 'nhắc', và BA đã xác nhận không có tool admin (C-CNL-03).</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>✅ Resolved 2026-09-17 (vòng 2) — → xem dòng "C-DLV-07 (vòng 2)"</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-23.2.01 (tr.25) · BR08-06 (tr.41) · BR09-04 (tr.42) · §8.13.1 (tr.47)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>(a) 'Nhắc' là push/in-app? Nội dung câu nhắc? Có phải loại thông báo thứ 16 chưa có trong danh mục?
 (b) 'Cuối ngày' là mấy giờ?
@@ -4120,46 +4561,51 @@
 (d) Các mốc 2h/4h/24h đã được build chưa — nếu chưa thì để out of scope?</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>SC-DLV-024/048/054 cần chờ thời gian thật mà không biết kết quả mong đợi</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1" s="12">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vào link demo, thao tác vào các btn, link  kiểm tra lại các ui còn thiến và đặt lại câu hỏi sau nhé </t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): đã rà toàn bộ các màn thao tác được (Chờ ghép/Đã ghép/Lấy hàng/Đang giao/Xác nhận đã giao/Liên hệ người gửi/Xử lý đơn hàng/Cầm hàng về) — KHÔNG thấy bất kỳ UI, banner, hay copy nào liên quan 'nhắc' (reminder) hay 'chuyển admin hỗ trợ'. Đây là rule time-based (2h/4h/24h) nên bản demo tĩnh (không có đồng hồ thật) không thể mô phỏng được — giữ nguyên câu hỏi gốc, cần BA/Dev trả lời trực tiếp bằng lời, không dùng demo để verify được.
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1" s="15">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-DLV-08</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Có 2 đường gửi hàng ở quầy: chọn 'Quầy lễ tân/Quầy bảo vệ' ngay ở màn Xác nhận giao hàng, hoặc qua 'Không liên lạc được → Xử lý đơn hàng'. PRD chỉ nói đường thứ 2 gắn cờ 'không liên lạc được' + NTF-11.</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Chờ BA — vòng 2 (đã đối chiếu ảnh DLV_03) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR07-01/BR07-05 (tr.39) · §8.7/§8.8 Post-Conditions (tr.39,41) · NTF-05/NTF-11 (tr.47)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Khi chọn quầy TRỰC TIẾP ở màn Xác nhận giao hàng:
 (a) có gắn cờ 'không liên lạc được người nhận' không?
@@ -4168,21 +4614,281 @@
 (d) có áp thời hạn giữ hàng tại quầy 4h/24h không?</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>SC-DLV-039 ⟷ SC-DLV-045 chưa phân biệt được kết quả</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Thấp</t>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vào link demo, thao tác vào các btn, link  kiểm tra lại các ui còn thiến và đặt lại câu hỏi sau nhé </t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>SỬA LẠI 2026-09-17 (rà lại 00_input/v1.1/design/DLV_03 — đã có sẵn từ 2026-09-15, lượt vibe-check hôm nay bỏ sót không đối chiếu trước khi thao tác lại): ảnh DLV_03 cho thấy CHỌN THẲNG 'Quầy lễ tân' ở màn 'Xác nhận đã giao' (đường thứ 2, không qua 'Không thể liên lạc') CŨNG hiện khối 'NGƯỜI NHẬN TẠI QUẦY' (Họ tên người trực quầy + SĐT) giống hệt đường thứ 1 (không liên lạc được) — vậy 2 đường đều đòi cùng bộ field bổ sung này ở bước chọn quầy, không có gì phân biệt hình thức giữa 2 đường ngoài việc có/không có cảnh báo 'Không thể liên lạc cho người nhận?' phía trên. Giữ nguyên câu hỏi gốc (a)(b)(c)(d) về flag/NTF — demo tĩnh không trả lời được, cần BA/Dev.
+— Ghi chú trước đó: CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): xác nhận có ĐƯỜNG THỨ 2 độc lập — ngay tại màn 'Xác nhận đã giao' (KHÔNG cần bấm 'Không thể liên lạc cho người nhận?'), field 'Giao cho *' đã có sẵn 4 lựa chọn: Người nhận / Người được uỷ quyền / Quầy lễ tân / Quầy bảo vệ — chọn thẳng 'Quầy lễ tân'/'Quầy bảo vệ' tại đây mà không qua luồng 'không liên lạc được'. Đây chính là đường BR07-01/BR07-05 mô tả. KHÔNG quan sát được (a)(b)(c)(d) vì demo tĩnh không có notification log / không hiển thị flag ẩn — cần BA/Dev trả lời trực tiếp: chọn quầy ở đường thứ 2 này có tự gắn cờ 'không liên lạc được người nhận' không, bắn NTF-05 hay NTF-11, có hiện dòng 'Uỷ quyền bởi: Người nhận' không, có áp hạn giữ hàng 4h/24h không.
+— Ghi chú trước đó: 🟢 Thấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="109.5" customHeight="1" s="15">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>C-DLV-05 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Câu (d) duy nhất còn lại: cơ chế chuyển trạng thái đúng giờ hẹn giao lại — tự động hay Carrier tự bấm; thanh tiến trình có mốc phụ cho "Hẹn giao lại"/"Đang hoàn hàng" không.</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved — QA tự verify qua demo 2026-09-17, không cần BA trả lời</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 §5.1 Timeline 5 mốc (tr.10) · vibe-check demo 2026-09-17: thanh tiến trình vẫn hiện "Đang giao" xuyên suốt</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Đến đúng giờ hẹn giao lại, đơn có TỰ ĐỘNG chuyển về "Đang giao" hay Carrier phải tự bấm nút? Thanh tiến trình 5 mốc (Chờ ghép/Lấy hàng/Đang giao/Đã giao/Hoàn thành) ở bản chính thức có được bổ sung nhãn phụ cho "Hẹn giao lại"/"Đang hoàn hàng" không, hay giữ nguyên hiện "Đang giao" như demo hiện tại?</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>SC-DLV-016 (timeline hiển thị) chưa assert được nhãn chính xác</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>BA/Dev</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">đúng nhé </t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>Duy nhất 1 câu còn lại của C-DLV-05 — (a)(b)(c) đã chốt qua demo 2026-09-17.
+⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2): DLV-giao-nhan/risk_assessment.md · C-DLV-05 ĐÓNG HẲN 2026-09-17 — timeline giữ 5 mốc cố định là chủ đích thiết kế. Không cần trả lời thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="149.25" customHeight="1" s="15">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>C-DLV-06 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Xác nhận cấu trúc 4 tầng đã map qua demo là CHUẨN CHÍNH THỨC (không phải giới hạn riêng của bản demo) + câu hỏi mới phát sinh về field "Người nhận tại quầy".</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved — QA tự verify qua demo 2026-09-17, không cần BA trả lời</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Ảnh 00_input/v1.1/design/DLV_04_lienhengnguoigui_khongthelienlac.png, DLV_05_xulydonhang_khongkiensile.png · vibe-check demo 2026-09-17</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>(1) Xác nhận cấu trúc màn "Không liên lạc được người nhận" là chuỗi 4 tầng: (a) màn "Xác nhận đã giao" → (b) màn "Liên hệ người gửi" (có sẵn lựa chọn giao cho Người được uỷ quyền/Quầy lễ tân/Quầy bảo vệ) → (c) modal "Chưa liên lạc được?" (2 nút: chờ &amp; gọi lại / xử lý đơn hàng) → (d) màn "Xử lý đơn hàng" (3 phương án theo thứ tự: Chốt bảo vệ → Quầy lễ tân → Cầm hàng về) — đây có đúng là thiết kế chính thức không? (2) Khi chọn "Quầy lễ tân"/"Quầy bảo vệ", 2 ô "Họ tên người trực quầy" và "Số điện thoại" hiện ra có BẮT BUỘC nhập không? Có dùng để gọi xác nhận lại không, hay chỉ lưu ghi chú?</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>SC-DLV-043 (oracle chính) + SC mới cho field "Người nhận tại quầy" chưa viết được</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiểm tra lại qua mcp cái nữa ??  trên ui có dâu * bắt buộc mà , thao tác từng cái và lưu lại ui cho t nhé 
+Chỉ lưu ghi chú nhé, chỉ người nhận mới được xác nhận </t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>Đã map rõ toàn bộ cấu trúc qua demo — chỉ cần BA xác nhận + trả lời 1 câu mới.
+⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2): DLV-giao-nhan/risk_assessment.md · C-DLV-06 ĐÓNG HẲN 2026-09-17 — đã tự verify qua demo: bỏ trống 2 ô bắt buộc thì form chặn submit, khớp câu trả lời BA. Không cần trả lời thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="109.5" customHeight="1" s="15">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>C-DLV-08 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>3 câu còn lại về flag/thông báo khi chọn quầy trực tiếp — không quan sát được qua demo tĩnh (không có notification log).</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>🟡 Partially — (d) đóng 2026-09-17 (out of scope); (a)(b) → xem dòng "C-DLV-08 (vòng 4)"</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 BR07-05 (tr.39) · §8.13.1 NTF-05/NTF-11 (tr.47) · vibe-check demo 2026-09-17: xác nhận 2 đường độc lập tồn tại</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Khi Carrier chọn "Quầy lễ tân"/"Quầy bảo vệ" TRỰC TIẾP ở màn "Xác nhận đã giao" (không qua "Không thể liên lạc được người nhận"): (a) đơn có tự gắn cờ "không liên lạc được người nhận" không? (b) gửi thông báo NTF-05 hay NTF-11? (c) có áp thời hạn giữ hàng tại quầy 4h/24h (BR08-06) không?</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>SC-DLV-039 ⟷ SC-DLV-045 chưa phân biệt được kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>BA/Dev</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>sẽ lưu thông tin tại Block lich sử nhé (có thể mở link demo để xem lại )</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2, SỬA LẠI ghi chú sai ở lượt trước — (a)(b)(c) CHƯA tự verify, đính chính): BA gợi ý câu trả lời (a)/(b) nằm trong log của block LỊCH SỬ trên màn Theo dõi đơn ("sẽ lưu thông tin tại Block lịch sử nhé") — QA CHƯA thao tác lại để đọc đúng câu log đó. Việc còn lại: QA tự vibe-check đọc log Block Lịch sử trước, chỉ hỏi BA phần KHÔNG đọc được qua log (chắc chắn là câu (c) thời hạn giữ hàng — rule time-based, log tĩnh không thể hiện được).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1" s="15">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>C-DLV-07 (vòng 2)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>BA trả lời trực tiếp bằng lời (demo tĩnh không mô phỏng được rule time-based): hệ quả quan sát được ở các mốc nhắc 2h/4h · 4h/cuối ngày/24h · 24h quá hẹn.</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>✅ Resolved 2026-09-17 — ĐÓNG HẲN</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 AC-23.2.01 (tr.25) · BR08-06 (tr.41) · BR09-04 (tr.42) · §8.13.1 danh mục 15 thông báo (tr.47)</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>(a) 'Nhắc' là push/in-app? Nội dung câu nhắc? Có phải loại thông báo thứ 16 chưa có trong danh mục?
+(b) 'Cuối ngày' là mấy giờ?
+(c) 'Chuyển admin hỗ trợ' có làm đơn đổi trạng thái / nhãn / cờ gì người dùng nhìn thấy không?
+(d) Các mốc 2h/4h/24h đã được build chưa — nếu chưa thì để out of scope?</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>SC-DLV-024 (v1.0) · SC-DLV-048 · SC-DLV-054 — trước đây không biết assert gì sau các mốc</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>BA/Dev</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>không chỉ gởi remind thôi nhé</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17 — ĐÓNG HẲN. Đọc đúng là "Không, CHỈ gửi remind thôi nhé" (QC GiangDC2 xác nhận nghĩa), khớp câu trả lời C-DLV-08 cùng lượt ("phase này các chỗ liên quan đến role admin chưa làm") và C-CNL-03 (không có màn/tool admin). ⇒ (c) Mọi mốc chỉ GỬI THÔNG BÁO NHẮC — đơn KHÔNG đổi trạng thái, KHÔNG gắn nhãn/cờ người dùng thấy được; vế "chuyển admin hỗ trợ" (AC-23.2.01 / BR08-06 / BR09-04) CHƯA BUILD ⇒ OUT OF SCOPE v1.1, không assert, không log bug khi không thấy. (d) SC-DLV-024/048/054 không còn chờ bề mặt admin; assert được ngay: đơn KHÔNG tự chuyển "Hoàn thành". ⚠️ Giới hạn đã biết, CHẤP NHẬN (không mở CL mới): (a) kênh nhắc (push/in-app) + nguyên văn câu nhắc chưa có đặc tả — danh mục 15 loại thông báo §8.13.1 vẫn không có loại "nhắc"; (b) "cuối ngày" chưa rõ mấy giờ. ⇒ TC assert "CÓ thông báo nhắc", GHI NHẬN kênh + nguyên văn + giờ thực tế; không assert giờ cụ thể, không FAIL vì kênh hiển thị. Canonical: v1.1/DLV-giao-nhan/risk_assessment.md mục "C-DLV-07 · ↳ BA trả lời 2026-09-17 (vòng 2)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="109.5" customHeight="1" s="15">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>C-DLV-08 (vòng 4)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Câu (d) còn lại: có áp thời hạn giữ hàng tại quầy 4h/24h (BR08-06) cho đường chọn quầy TRỰC TIẾP không — và hệ quả "chuyển admin hỗ trợ" là gì.</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved 2026-09-17 — (d) ĐÓNG (out of scope); còn (a)(b) QA TỰ XÁC MINH, KHÔNG hỏi BA nữa</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 BR08-06 (tr.41) · BR07-05 (tr.39) · §8.13.1 NTF-05/NTF-11 (tr.47)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>(d) Đường chọn quầy trực tiếp ở màn "Xác nhận đã giao" có áp hạn giữ hàng 4h/24h + chuyển admin như BR08-06 không?</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>SC-DLV-039 ⟷ SC-DLV-045 (phân biệt 2 đường) · SC-DLV-048 (hạn giữ hàng)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>BA/Dev</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>phase này các chỗ liên quan đến role admin chưa làm nhé</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (theo BA) 2026-09-17: (d) thời hạn giữ hàng tại quầy 4h/24h → chuyển admin (BR08-06) OUT OF SCOPE v1.1 — mọi bề mặt role admin chưa build ở phase này (khớp C-DLV-07 "chỉ gửi remind" + C-CNL-03 "dev xử lý tay ngoài app"). ⇒ SC-DLV-039/045 KHÔNG assert hạn giữ hàng/chuyển admin; SC-DLV-048 chỉ assert 2 mốc nhắc. CÒN TREO (a)(b) — đường chọn quầy trực tiếp có gắn cờ "không liên lạc được" không, bắn NTF-05 hay NTF-11: BA đã chỉ chỗ tự đọc ở vòng 3 ("sẽ lưu thông tin tại Block lịch sử") ⇒ KHÔNG hỏi BA nữa, QA vibe-check: chọn "Quầy lễ tân"/"Quầy bảo vệ" trực tiếp ở màn "Xác nhận đã giao" → mở block LỊCH SỬ ở màn Theo dõi đơn → đọc câu log. Trước khi có kết quả đó: SC-DLV-039/045 GHI NHẬN, không assert cờ/NTF. Canonical: v1.1/DLV-giao-nhan/risk_assessment.md mục "C-DLV-08 · ↳ BA trả lời 2026-09-17 (vòng 4)".</t>
         </is>
       </c>
     </row>
@@ -4203,155 +4909,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="11" min="1" max="1"/>
-    <col width="42" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="26" customWidth="1" style="11" min="4" max="4"/>
-    <col width="50" customWidth="1" style="11" min="5" max="5"/>
-    <col width="32" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="40" customWidth="1" style="11" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" customWidth="1" style="14" min="2" max="2"/>
+    <col width="16" customWidth="1" style="14" min="3" max="3"/>
+    <col width="26" customWidth="1" style="14" min="4" max="4"/>
+    <col width="50" customWidth="1" style="14" min="5" max="5"/>
+    <col width="32" customWidth="1" style="14" min="6" max="6"/>
+    <col width="14" customWidth="1" style="14" min="7" max="7"/>
+    <col width="40" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="14" min="9" max="9"/>
+    <col width="30" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="12">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="15">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>TS-trust-safety — Trust &amp; Safety (Báo cáo sự cố)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="12">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="15">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Các điểm chưa rõ cần hỏi BA · cập nhật 2026-09-16 sau khi BA trả lời lượt 1 · Dòng 'vòng 2' = hỏi tiếp trên câu BA đã trả lời · Dòng 'Open (mới)' = phát hiện khi rà sâu PRD ⟷ scenario. Điền cột 'Câu trả lời BA' / 'Ngày trả lời'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="15">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>CL ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Vấn đề / Nội dung chưa rõ</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Nguồn tài liệu (DOC/section)</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Câu hỏi cụ thể cho BA</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Ảnh hưởng nếu chưa chốt (SC/TC treo)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Hỏi ai</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Câu trả lời BA</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Ngày trả lời</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="120" customHeight="1" s="12">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="120" customHeight="1" s="15">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-TS-02</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>AC-31.1.01: nút 'Báo cáo sự cố' ở màn theo dõi đơn với vai trò bất kỳ; §8.12.3 chỉ liệt kê 'Báo sự cố' ở Đang giao (3 vai) và Đã giao (chỉ Người gửi). Từ điển: 'Có sự cố' = có báo cáo sự cố sau Đang giao; S-14 viết 'có thể chuyển'; BA (C-CNL-03) nói dev xử lý tay qua Google Form — form Google không gọi được API app.</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>✅ Resolved (qua vibe-check demo 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 AC-31.1.01 (tr.29) · §8.12.2/§8.12.3 (tr.45-46) · §5.2 S-14 (tr.12) · BA trả lời C-CNL-03</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>(a) Nút 'Báo cáo sự cố' hiện ở những trạng thái nào (Chờ ghép? Đã ghép? Hoàn thành / đơn đã đóng?) và cho vai nào?
 (b) Gửi form có TỰ chuyển đơn sang 'Có sự cố' không? Nếu không, ai đưa đơn vào trạng thái này? Nếu không ai thì trạng thái 'Có sự cố' không bao giờ xuất hiện trên app?
 (c) Loại yêu cầu 'Lỗi ứng dụng' / 'Góp ý' có làm đơn đổi trạng thái không?</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>🔴 SC-TS-015, SC-CNL-006, SC-CNL-015, SC-DLV-034 — nếu không có đường vào 'Có sự cố' thì 2 SC sau out of scope</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>🔴 Cao — trước generate-tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1" s="12">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a, vào demo coi xem đươc không 
+b ver hiện tại không chuyển trạng thái gì
+c. Khong  </t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN (vibe-check demo QA GiangDC2, 2026-09-17): (a) XÁC NHẬN qua demo — nút 'Báo cáo sự cố' HIỆN Ở MỌI TRẠNG THÁI đã thử (Chờ ghép, Đã ghép, Đang giao) và cho MỌI VAI (Người gửi, Người vận chuyển) — không giới hạn theo §8.12.3 như PRD liệt kê. (b)(c) khớp câu trả lời BA — đã thao tác thật: gửi form 'Báo cáo sự cố' xong, bấm 'Quay lại đơn hàng' thì quay đúng về 'Theo dõi đơn' và trạng thái đơn KHÔNG đổi (vẫn 'Chờ ghép') — xác nhận 'ver hiện tại không chuyển trạng thái gì'. CL-TS-02 ĐÓNG HẲN.
+— Ghi chú trước đó: 🔴 Cao — trước generate-tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1" s="15">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>C-TS-03</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>3 mâu thuẫn trong FR16: BR16-02 chỉ đẩy MÃ ĐƠN ⟷ AC-31.1.01 prefill 9 trường; §8.16.2 mã đơn 'Chỉ đọc · Không sửa' ⟷ BR16-03 'trường prefill người dùng vẫn sửa được' (Google Form không khoá được); BR16-01 dùng Custom Tabs / SFSafariViewController — app không vẽ được nút 'Thử lại' khi mất mạng, và nút 'Quay lại đơn hàng' trên trang Google Form không điều khiển được app.</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>🔴 Open (mới)</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>🟡 Partially Resolved — hỏi vòng 2 (đã vibe-check demo) — → xem vòng 3 (dòng cuối sheet, đã tách câu hỏi còn lại)</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>DOC-v1.1-01 BR16-01..04 (tr.50) · §8.16.2 (tr.51) · AC-31.1.01/31.2.01 (tr.29-30) · ảnh TS_02</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>(a) Form prefill những trường nào: chỉ mã đơn hay đủ 9 trường?
 (b) Mã đơn chỉ đọc hay người dùng sửa được?
@@ -4359,31 +5072,88 @@
 (d) Nút 'Thử lại' (mất mạng) và 'Quay lại đơn hàng' (sau khi gửi) do APP hay GOOGLE FORM hiển thị?</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>SC-TS-008/012/014 chưa assert được</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>BA/Dev</t>
         </is>
       </c>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Trung bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1" s="12"/>
-    <row r="7" ht="120" customHeight="1" s="12"/>
-    <row r="8" ht="120" customHeight="1" s="12"/>
-    <row r="9" ht="120" customHeight="1" s="12"/>
-    <row r="10" ht="120" customHeight="1" s="12"/>
-    <row r="11" ht="120" customHeight="1" s="12"/>
-    <row r="12" ht="120" customHeight="1" s="12"/>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a. mã đơn
+b. chỉ đoc
+c. nhung link docs.google.com/forms/foxeco-ho-tro
+d. không rõ, dev xử lý sao cũng được, btn Quay lại đơn hàng thì thao tác thêm trên demo để biết nhé </t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>SỬA LẠI 2026-09-17 (đối chiếu 00_input/v1.1/design/TS_02 — đã có sẵn từ 2026-09-15): ảnh TS_02 cho thấy khung nhúng có icon '✕' (đóng) ở góc trái + THANH ĐỊA CHỈ hiện rõ 'docs.google.com/forms/foxeco-ho-tro' — đây là kiểu chrome đặc trưng của Custom Tabs/SFSafariViewController (không phải WebView trần, WebView thường không tự vẽ thanh địa chỉ), nên NHIỀU KHẢ NĂNG ý định thiết kế là Custom Tabs. Đây vẫn là mock tĩnh nên chưa chắc chắn 100% — đề nghị Dev xác nhận thẳng để chốt (c), ảnh hưởng trực tiếp khả năng vẽ nút 'Thử lại' khi mất mạng (SC-TS-008/012).
+— Ghi chú trước đó: CẬP NHẬT 2026-09-17 (vibe-check demo QA GiangDC2): (a) XÁC NHẬN — form demo chỉ prefill đúng 1 trường 'Mã đơn hàng' (hiện text tĩnh 'FE-2508-0472', ghi chú 'Tự động điền từ ứng dụng'); các trường khác (Loại yêu cầu / Mô tả chi tiết / SĐT liên hệ) đều TRỐNG, phải nhập tay — khớp đúng câu trả lời BA 'a. mã đơn'. (b) XÁC NHẬN — ô 'Mã đơn hàng' hiển thị dạng nhãn tĩnh (không phải textbox, không bấm sửa được) → CHỈ ĐỌC, khớp câu trả lời BA 'b. chỉ đọc'. (d, phần 'ai hiển thị nút') XÁC NHẬN — sau khi bấm 'Gửi', màn 'Đã ghi nhận phản hồi' + nút 'Quay lại đơn hàng' là do CHÍNH APP hiển thị (giao diện native cùng theme với app, không phải trang xác nhận của Google Form) và bấm vào quay thẳng về 'Theo dõi đơn' — vậy nút này do APP điều khiển, không phải Google Form tự sinh link quay lại. CÒN TREO: (c) kỹ thuật nhúng thật (WebView nhúng hay Custom Tabs/SFSafariViewController) — demo chỉ mock 1 thanh tiêu đề hiện text URL 'docs.google.com/forms/foxeco-ho-tro', không chứng minh được công nghệ thật, cần Dev xác nhận trực tiếp (quyết định này ảnh hưởng liệu nút 'Thử lại' khi mất mạng có vẽ được không — SC-TS-008/012).
+— Ghi chú trước đó: 🟡 Trung bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="109.5" customHeight="1" s="15">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>C-TS-03 (vòng 3)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Câu (c) duy nhất còn lại: công nghệ nhúng thật của WebView "Báo cáo sự cố" (WebView trần hay Custom Tabs/SFSafariViewController) — ảnh demo TS_02 gợi ý Custom Tabs (có icon ✕ + thanh địa chỉ) nhưng chưa chắc chắn 100%.</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>✅ Resolved — QA tự verify qua demo 2026-09-17, không cần BA trả lời</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>DOC-v1.1-01 BR16-01 (tr.50) · ảnh 00_input/v1.1/design/TS_02_baocaosucos_form_googleform.png</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>App đang mở màn "Báo cáo sự cố" bằng WebView nhúng thường hay bằng Custom Tabs/SFSafariViewController (trình duyệt hệ thống)? Câu trả lời ảnh hưởng trực tiếp: nếu là Custom Tabs, app không tự vẽ được nút "Thử lại" khi mất mạng bên trong khung đó — vậy nút này (nếu có) do ai hiển thị?</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>SC-TS-012 (nút Thử lại khi mất mạng) chưa assert được ai hiển thị</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App hiên thi nhé </t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>Duy nhất 1 câu còn lại của C-TS-03 — (a)(b)(d) đã Resolved 2026-09-17 qua demo.
+⛔ CẬP NHẬT 2026-09-17 (QA GiangDC2): TS-trust-safety/risk_assessment.md · C-TS-03 ĐÓNG HẲN 2026-09-17 — Dev: nút 'Thử lại' do APP hiển thị. Không cần trả lời thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" s="15"/>
+    <row r="8" ht="120" customHeight="1" s="15"/>
+    <row r="9" ht="120" customHeight="1" s="15"/>
+    <row r="10" ht="120" customHeight="1" s="15"/>
+    <row r="11" ht="120" customHeight="1" s="15"/>
+    <row r="12" ht="120" customHeight="1" s="15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
